--- a/resampling/input/accessibility_reports_generated/INTERSOS_accessibility_report.xlsx
+++ b/resampling/input/accessibility_reports_generated/INTERSOS_accessibility_report.xlsx
@@ -184,8 +184,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="WardAccessibility" displayName="WardAccessibility" ref="A1:Q52" headerRowCount="1">
-  <autoFilter ref="A1:Q52"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="WardAccessibility" displayName="WardAccessibility" ref="A1:Q117" headerRowCount="1">
+  <autoFilter ref="A1:Q117"/>
   <tableColumns count="17">
     <tableColumn id="1" name="State"/>
     <tableColumn id="2" name="LGA"/>
@@ -210,8 +210,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="ClusterAccessibility" displayName="ClusterAccessibility" ref="A1:O84" headerRowCount="1">
-  <autoFilter ref="A1:O84"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="ClusterAccessibility" displayName="ClusterAccessibility" ref="A1:O77" headerRowCount="1">
+  <autoFilter ref="A1:O77"/>
   <tableColumns count="15">
     <tableColumn id="1" name="State"/>
     <tableColumn id="2" name="LGA"/>
@@ -553,7 +553,7 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Assigned to you: 51 wards, 83 clusters</t>
+          <t>Assigned to you: 116 wards, 76 clusters</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q52"/>
+  <dimension ref="A1:Q117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -849,13 +849,13 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J2" t="n">
-        <v>60</v>
+        <v>107</v>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
@@ -878,12 +878,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Gajiganna</t>
+          <t>Hoyo Chingua</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Gajigana</t>
+          <t>Hoyo Chingowa</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nganzai</t>
+          <t>Konduga</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -902,13 +902,13 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>54</v>
+        <v>24</v>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
@@ -931,12 +931,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Kalizoram</t>
+          <t>Ardoram</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Kalizoram</t>
+          <t>Ardoram</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -947,13 +947,13 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
@@ -976,29 +976,37 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Titiwa</t>
+          <t>Gubio 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Titiwa</t>
+          <t>Furram</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Gubio; Nganzai</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
@@ -1021,12 +1029,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ngulabamma</t>
+          <t>Kareram</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Kupti</t>
+          <t>Kararam</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1037,13 +1045,13 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
@@ -1066,29 +1074,33 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ngamma</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Ngamma</t>
-        </is>
-      </c>
+          <t>Ardimini</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Gubio</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
@@ -1111,29 +1123,33 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Kupti</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Kupti</t>
-        </is>
-      </c>
+          <t>Auno</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Jere; Konduga; Maiduguri</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
@@ -1156,14 +1172,10 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Borno Yesu</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Borno Yesu</t>
-        </is>
-      </c>
+          <t>Ayi Yasku</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
           <t>No</t>
@@ -1172,13 +1184,13 @@
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
@@ -1201,29 +1213,33 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Furram</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Furram</t>
-        </is>
-      </c>
+          <t>Borko</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Gubio</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
@@ -1246,14 +1262,10 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sasawa / Kabaru</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Kalizoram</t>
-        </is>
-      </c>
+          <t>Borno Yesu</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>No</t>
@@ -1262,13 +1274,13 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
@@ -1291,31 +1303,19 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Miye</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Gajigana</t>
-        </is>
-      </c>
+          <t>Furram</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Mafa; Nganzai</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -1339,34 +1339,38 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Maiduguri</t>
+          <t>Magumeri</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Maisandari</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Maisandari</t>
-        </is>
-      </c>
+          <t>Gadai</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Gubio; Nganzai</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H13" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
@@ -1384,34 +1388,38 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Maiduguri</t>
+          <t>Magumeri</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Bolori 2</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Bolori II</t>
-        </is>
-      </c>
+          <t>Gajiganna</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Konduga; Nganzai</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
@@ -1429,34 +1437,38 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Maiduguri</t>
+          <t>Magumeri</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Bolori 1</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Bolori I</t>
-        </is>
-      </c>
+          <t>Gamawo</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Gubio</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
@@ -1474,34 +1486,38 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Maiduguri</t>
+          <t>Magumeri</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Gwange 3</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Gwange III</t>
-        </is>
-      </c>
+          <t>Jakana</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Kaga; Konduga</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
@@ -1519,34 +1535,38 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Maiduguri</t>
+          <t>Magumeri</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Gwange 2</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Gwange II</t>
-        </is>
-      </c>
+          <t>Kalizoram</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Konduga</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
@@ -1564,34 +1584,38 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Maiduguri</t>
+          <t>Magumeri</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Lamisula</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Lamisula</t>
-        </is>
-      </c>
+          <t>Karagawaru</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Kaga; Konduga</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
@@ -1609,19 +1633,15 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Maiduguri</t>
+          <t>Magumeri</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Bulabulin</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Bulabulin</t>
-        </is>
-      </c>
+          <t>Kukareta Warsala</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -1629,7 +1649,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gwoza</t>
+          <t>Kaga</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1638,13 +1658,13 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
@@ -1662,42 +1682,30 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Maiduguri</t>
+          <t>Magumeri</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Galtimari</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Maisandari</t>
-        </is>
-      </c>
+          <t>Kupti</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Jere</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
@@ -1715,19 +1723,15 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Maiduguri</t>
+          <t>Magumeri</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Gamboru</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Gamboru</t>
-        </is>
-      </c>
+          <t>Mafa</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -1735,7 +1739,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Jere</t>
+          <t>Konduga; Mafa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1744,13 +1748,13 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
@@ -1768,34 +1772,38 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Maiduguri</t>
+          <t>Magumeri</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Gwange 1</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Gwange I</t>
-        </is>
-      </c>
+          <t>Miye</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Mafa; Nganzai</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
@@ -1813,34 +1821,38 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Maiduguri</t>
+          <t>Magumeri</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Hausari</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Hausari</t>
-        </is>
-      </c>
+          <t>Ngamdu</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Kaga</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
@@ -1858,19 +1870,15 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Maiduguri</t>
+          <t>Magumeri</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Limanti</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Limanti</t>
-        </is>
-      </c>
+          <t>Ngamma</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -1878,7 +1886,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bayo; Jere; Mafa</t>
+          <t>Gubio</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1887,13 +1895,13 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
@@ -1911,34 +1919,38 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Maiduguri</t>
+          <t>Magumeri</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Mafoni</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Mafoni</t>
-        </is>
-      </c>
+          <t>Ngulabamma</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Gubio</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
@@ -1956,19 +1968,15 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Maiduguri</t>
+          <t>Magumeri</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Yajiwa</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Bolori I</t>
-        </is>
-      </c>
+          <t>Sasawa / Kabaru</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
           <t>No</t>
@@ -1977,13 +1985,13 @@
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
@@ -2001,19 +2009,15 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Maiduguri</t>
+          <t>Magumeri</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Dala</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Maisandari</t>
-        </is>
-      </c>
+          <t>Titiwa</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -2021,7 +2025,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Jere</t>
+          <t>Konduga; Nganzai</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2030,13 +2034,13 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
@@ -2059,29 +2063,37 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Fezzan</t>
+          <t>Maisandari</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Fezzan</t>
+          <t>Maisandari</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Jere</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H28" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J28" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
@@ -2104,29 +2116,37 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Shehuri North</t>
+          <t>Bolori 2</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Shehuri North</t>
+          <t>Bolori II</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Jere</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J29" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
@@ -2139,20 +2159,24 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Zamfara</t>
+          <t>Borno</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Gusau</t>
+          <t>Maiduguri</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Galadima</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
+          <t>Bolori 1</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Bolori I</t>
+        </is>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -2160,7 +2184,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Anka; Bakura; Talata Mafara</t>
+          <t>Konduga</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2169,13 +2193,13 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J30" t="n">
-        <v>62</v>
+        <v>2</v>
       </c>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
@@ -2188,43 +2212,39 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Zamfara</t>
+          <t>Borno</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Gusau</t>
+          <t>Maiduguri</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Tudun Wada</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr"/>
+          <t>Mafoni</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Mafoni</t>
+        </is>
+      </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Bungudu</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
       <c r="H31" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I31" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>54</v>
+        <v>2</v>
       </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
@@ -2237,35 +2257,47 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Zamfara</t>
+          <t>Borno</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Gusau</t>
+          <t>Maiduguri</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Wanke</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr"/>
+          <t>Bulabulin</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Bulabulin</t>
+        </is>
+      </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Gwoza</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I32" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
@@ -2278,20 +2310,24 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Zamfara</t>
+          <t>Borno</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Gusau</t>
+          <t>Maiduguri</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Mada</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr"/>
+          <t>Fezzan</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Fezzan</t>
+        </is>
+      </c>
       <c r="E33" t="inlineStr">
         <is>
           <t>No</t>
@@ -2300,13 +2336,13 @@
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="n">
         <v>1</v>
-      </c>
-      <c r="J33" t="n">
-        <v>12</v>
       </c>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
@@ -2319,35 +2355,47 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Zamfara</t>
+          <t>Borno</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Gusau</t>
+          <t>Maiduguri</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Magami</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr"/>
+          <t>Lamisula</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Lamisula</t>
+        </is>
+      </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Jere</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H34" t="n">
+        <v>3</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="n">
         <v>1</v>
-      </c>
-      <c r="I34" t="n">
-        <v>1</v>
-      </c>
-      <c r="J34" t="n">
-        <v>12</v>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
@@ -2360,35 +2408,47 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Zamfara</t>
+          <t>Borno</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Gusau</t>
+          <t>Maiduguri</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Madawaki</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr"/>
+          <t>Limanti</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Limanti</t>
+        </is>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Bayo; Jere; Mafa</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I35" t="n">
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
@@ -2401,20 +2461,24 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Zamfara</t>
+          <t>Borno</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Gusau</t>
+          <t>Maiduguri</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Mayana</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr"/>
+          <t>Yajiwa</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Bolori I</t>
+        </is>
+      </c>
       <c r="E36" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -2422,7 +2486,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bungudu</t>
+          <t>Jere; Konduga</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2437,7 +2501,7 @@
         <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
@@ -2450,35 +2514,43 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Zamfara</t>
+          <t>Borno</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Gusau</t>
+          <t>Maiduguri</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Ruwan Bore</t>
+          <t>Auno</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Jere; Konduga; Magumeri</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I37" t="n">
         <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
@@ -2491,27 +2563,39 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Zamfara</t>
+          <t>Borno</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Gusau</t>
+          <t>Maiduguri</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Wonaka</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr"/>
+          <t>Dala</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Maisandari</t>
+        </is>
+      </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Jere; Konduga</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H38" t="n">
         <v>1</v>
       </c>
@@ -2519,7 +2603,7 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
@@ -2532,35 +2616,47 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Zamfara</t>
+          <t>Borno</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Gusau</t>
+          <t>Maiduguri</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Rijiya</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr"/>
+          <t>Galtimari</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Maisandari</t>
+        </is>
+      </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Jere</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H39" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I39" t="n">
         <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
@@ -2573,20 +2669,24 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Zamfara</t>
+          <t>Borno</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Gusau</t>
+          <t>Maiduguri</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Furfuri Kwaikwai</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr"/>
+          <t>Gamboru</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Gamboru</t>
+        </is>
+      </c>
       <c r="E40" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -2594,7 +2694,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bungudu</t>
+          <t>Jere</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2609,7 +2709,7 @@
         <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
@@ -2622,35 +2722,43 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Zamfara</t>
+          <t>Borno</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Gusau</t>
+          <t>Maiduguri</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Sabon Gari</t>
+          <t>Gomari</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Jere; Konduga</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
@@ -2663,17 +2771,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Zamfara</t>
+          <t>Borno</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Gusau</t>
+          <t>Maiduguri</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Bela Rawaiya</t>
+          <t>Gongolong</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
@@ -2684,7 +2792,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bungudu; Kaura Namoda</t>
+          <t>Jere</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2693,7 +2801,7 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
@@ -2712,35 +2820,47 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Zamfara</t>
+          <t>Borno</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Maru</t>
+          <t>Maiduguri</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Kanoma</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr"/>
+          <t>Gwange 1</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Gwange I</t>
+        </is>
+      </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Jere</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H43" t="n">
         <v>1</v>
       </c>
       <c r="I43" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
@@ -2753,35 +2873,47 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Zamfara</t>
+          <t>Borno</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Maru</t>
+          <t>Maiduguri</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Dansadau</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr"/>
+          <t>Gwange 2</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Gwange II</t>
+        </is>
+      </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Jere</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H44" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
@@ -2794,35 +2926,47 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Zamfara</t>
+          <t>Borno</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Maru</t>
+          <t>Maiduguri</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Kuyanbana</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr"/>
+          <t>Gwange 3</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Gwange III</t>
+        </is>
+      </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Jere</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H45" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J45" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
@@ -2835,43 +2979,39 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Zamfara</t>
+          <t>Borno</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Maru</t>
+          <t>Maiduguri</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Ruwan Doruma</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr"/>
+          <t>Hausari</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Hausari</t>
+        </is>
+      </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Bungudu</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr"/>
       <c r="H46" t="n">
         <v>1</v>
       </c>
       <c r="I46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
@@ -2884,35 +3024,43 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Zamfara</t>
+          <t>Borno</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Maru</t>
+          <t>Maiduguri</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Bindin</t>
+          <t>Maimusari</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Jere</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J47" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
@@ -2925,35 +3073,43 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Zamfara</t>
+          <t>Borno</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Maru</t>
+          <t>Maiduguri</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Dangulbi</t>
+          <t>Mairi</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Jere; Konduga</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H48" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J48" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
@@ -2966,17 +3122,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Zamfara</t>
+          <t>Borno</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Maru</t>
+          <t>Maiduguri</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Maru</t>
+          <t>Mashamari</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
@@ -2987,7 +3143,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Bungudu</t>
+          <t>Jere</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -2999,10 +3155,10 @@
         <v>0</v>
       </c>
       <c r="I49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J49" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
@@ -3015,35 +3171,43 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Zamfara</t>
+          <t>Borno</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Maru</t>
+          <t>Maiduguri</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Bingi</t>
+          <t>Old Maiduguri</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Jere</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H50" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I50" t="n">
         <v>0</v>
       </c>
       <c r="J50" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
@@ -3056,17 +3220,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Zamfara</t>
+          <t>Borno</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Maru</t>
+          <t>Maiduguri</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Dankurmi</t>
+          <t>Shehuri North</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
@@ -3078,13 +3242,13 @@
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I51" t="n">
         <v>0</v>
       </c>
       <c r="J51" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
@@ -3097,17 +3261,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Zamfara</t>
+          <t>Borno</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Maru</t>
+          <t>Maiduguri</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Mayanchi</t>
+          <t>Shehuri South</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
@@ -3122,10 +3286,10 @@
         <v>0</v>
       </c>
       <c r="I52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J52" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
@@ -3135,23 +3299,3080 @@
       <c r="P52" t="inlineStr"/>
       <c r="Q52" t="inlineStr"/>
     </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Gusau</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Galadima</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Anka; Bakura; Bungudu; Talata Mafara</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H53" t="n">
+        <v>5</v>
+      </c>
+      <c r="I53" t="n">
+        <v>5</v>
+      </c>
+      <c r="J53" t="n">
+        <v>7</v>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" s="10" t="inlineStr"/>
+      <c r="P53" t="inlineStr"/>
+      <c r="Q53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Gusau</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Mayana</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Bungudu</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H54" t="n">
+        <v>2</v>
+      </c>
+      <c r="I54" t="n">
+        <v>1</v>
+      </c>
+      <c r="J54" t="n">
+        <v>7</v>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" s="10" t="inlineStr"/>
+      <c r="P54" t="inlineStr"/>
+      <c r="Q54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Gusau</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Tudun Wada</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Bungudu</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H55" t="n">
+        <v>5</v>
+      </c>
+      <c r="I55" t="n">
+        <v>3</v>
+      </c>
+      <c r="J55" t="n">
+        <v>7</v>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" s="10" t="inlineStr"/>
+      <c r="P55" t="inlineStr"/>
+      <c r="Q55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Gusau</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Madawaki</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="n">
+        <v>2</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" t="n">
+        <v>2</v>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" s="10" t="inlineStr"/>
+      <c r="P56" t="inlineStr"/>
+      <c r="Q56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Gusau</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Furfuri Kwaikwai</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Bungudu</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" t="n">
+        <v>1</v>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" s="10" t="inlineStr"/>
+      <c r="P57" t="inlineStr"/>
+      <c r="Q57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Gusau</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Bela Rawaiya</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Bungudu; Kaura Namoda</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H58" t="n">
+        <v>1</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" t="n">
+        <v>0</v>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" s="10" t="inlineStr"/>
+      <c r="P58" t="inlineStr"/>
+      <c r="Q58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Gusau</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Bingi North</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Bungudu; Maru</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H59" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" t="n">
+        <v>0</v>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" s="10" t="inlineStr"/>
+      <c r="P59" t="inlineStr"/>
+      <c r="Q59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Gusau</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Bingi South</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Bungudu; Maru</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H60" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" t="n">
+        <v>0</v>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
+      <c r="O60" s="10" t="inlineStr"/>
+      <c r="P60" t="inlineStr"/>
+      <c r="Q60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Gusau</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Dandire A</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="n">
+        <v>0</v>
+      </c>
+      <c r="I61" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" t="n">
+        <v>0</v>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
+      <c r="O61" s="10" t="inlineStr"/>
+      <c r="P61" t="inlineStr"/>
+      <c r="Q61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Gusau</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Dandire B</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Birnin Magaji</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H62" t="n">
+        <v>0</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" t="n">
+        <v>0</v>
+      </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
+      <c r="O62" s="10" t="inlineStr"/>
+      <c r="P62" t="inlineStr"/>
+      <c r="Q62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Gusau</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Danjibga</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Tsafe</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H63" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" t="n">
+        <v>0</v>
+      </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
+      <c r="O63" s="10" t="inlineStr"/>
+      <c r="P63" t="inlineStr"/>
+      <c r="Q63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Gusau</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Dansadau</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Maru; Tsafe</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H64" t="n">
+        <v>0</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" t="n">
+        <v>0</v>
+      </c>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
+      <c r="O64" s="10" t="inlineStr"/>
+      <c r="P64" t="inlineStr"/>
+      <c r="Q64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Gusau</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Dugu Muazu</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="n">
+        <v>0</v>
+      </c>
+      <c r="I65" t="n">
+        <v>0</v>
+      </c>
+      <c r="J65" t="n">
+        <v>0</v>
+      </c>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
+      <c r="O65" s="10" t="inlineStr"/>
+      <c r="P65" t="inlineStr"/>
+      <c r="Q65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Gusau</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Gusami Hayi</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Birnin Magaji; Kaura Namoda</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H66" t="n">
+        <v>0</v>
+      </c>
+      <c r="I66" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" t="n">
+        <v>0</v>
+      </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
+      <c r="O66" s="10" t="inlineStr"/>
+      <c r="P66" t="inlineStr"/>
+      <c r="Q66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Gusau</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Keta</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Tsafe</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H67" t="n">
+        <v>0</v>
+      </c>
+      <c r="I67" t="n">
+        <v>0</v>
+      </c>
+      <c r="J67" t="n">
+        <v>0</v>
+      </c>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
+      <c r="O67" s="10" t="inlineStr"/>
+      <c r="P67" t="inlineStr"/>
+      <c r="Q67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Gusau</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Kotorkoshi</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Bungudu; Tsafe</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H68" t="n">
+        <v>0</v>
+      </c>
+      <c r="I68" t="n">
+        <v>0</v>
+      </c>
+      <c r="J68" t="n">
+        <v>0</v>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
+      <c r="O68" s="10" t="inlineStr"/>
+      <c r="P68" t="inlineStr"/>
+      <c r="Q68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Gusau</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Kuyello</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Maru</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H69" t="n">
+        <v>0</v>
+      </c>
+      <c r="I69" t="n">
+        <v>0</v>
+      </c>
+      <c r="J69" t="n">
+        <v>0</v>
+      </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
+      <c r="O69" s="10" t="inlineStr"/>
+      <c r="P69" t="inlineStr"/>
+      <c r="Q69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Gusau</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Kwaren Ganuwa</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Tsafe</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H70" t="n">
+        <v>0</v>
+      </c>
+      <c r="I70" t="n">
+        <v>0</v>
+      </c>
+      <c r="J70" t="n">
+        <v>0</v>
+      </c>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
+      <c r="O70" s="10" t="inlineStr"/>
+      <c r="P70" t="inlineStr"/>
+      <c r="Q70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Gusau</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Mada</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Tsafe</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H71" t="n">
+        <v>0</v>
+      </c>
+      <c r="I71" t="n">
+        <v>0</v>
+      </c>
+      <c r="J71" t="n">
+        <v>0</v>
+      </c>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
+      <c r="O71" s="10" t="inlineStr"/>
+      <c r="P71" t="inlineStr"/>
+      <c r="Q71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Gusau</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Magami</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Bungudu; Maru; Tsafe</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H72" t="n">
+        <v>0</v>
+      </c>
+      <c r="I72" t="n">
+        <v>0</v>
+      </c>
+      <c r="J72" t="n">
+        <v>0</v>
+      </c>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
+      <c r="O72" s="10" t="inlineStr"/>
+      <c r="P72" t="inlineStr"/>
+      <c r="Q72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Gusau</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Maidabino B</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="n">
+        <v>0</v>
+      </c>
+      <c r="I73" t="n">
+        <v>0</v>
+      </c>
+      <c r="J73" t="n">
+        <v>0</v>
+      </c>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
+      <c r="O73" s="10" t="inlineStr"/>
+      <c r="P73" t="inlineStr"/>
+      <c r="Q73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Gusau</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Rijiya</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Bungudu; Tsafe</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H74" t="n">
+        <v>0</v>
+      </c>
+      <c r="I74" t="n">
+        <v>0</v>
+      </c>
+      <c r="J74" t="n">
+        <v>0</v>
+      </c>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
+      <c r="O74" s="10" t="inlineStr"/>
+      <c r="P74" t="inlineStr"/>
+      <c r="Q74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Gusau</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Ruwan Bore</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="n">
+        <v>0</v>
+      </c>
+      <c r="I75" t="n">
+        <v>0</v>
+      </c>
+      <c r="J75" t="n">
+        <v>0</v>
+      </c>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
+      <c r="O75" s="10" t="inlineStr"/>
+      <c r="P75" t="inlineStr"/>
+      <c r="Q75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Gusau</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Sabon Gari</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="n">
+        <v>1</v>
+      </c>
+      <c r="I76" t="n">
+        <v>0</v>
+      </c>
+      <c r="J76" t="n">
+        <v>0</v>
+      </c>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
+      <c r="O76" s="10" t="inlineStr"/>
+      <c r="P76" t="inlineStr"/>
+      <c r="Q76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Gusau</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Sabon Layi</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Tsafe</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H77" t="n">
+        <v>0</v>
+      </c>
+      <c r="I77" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" t="n">
+        <v>0</v>
+      </c>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
+      <c r="O77" s="10" t="inlineStr"/>
+      <c r="P77" t="inlineStr"/>
+      <c r="Q77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Gusau</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Sankalawa</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Bungudu</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H78" t="n">
+        <v>0</v>
+      </c>
+      <c r="I78" t="n">
+        <v>0</v>
+      </c>
+      <c r="J78" t="n">
+        <v>0</v>
+      </c>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
+      <c r="O78" s="10" t="inlineStr"/>
+      <c r="P78" t="inlineStr"/>
+      <c r="Q78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Gusau</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Tabanni</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="n">
+        <v>0</v>
+      </c>
+      <c r="I79" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" t="n">
+        <v>0</v>
+      </c>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
+      <c r="O79" s="10" t="inlineStr"/>
+      <c r="P79" t="inlineStr"/>
+      <c r="Q79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Gusau</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Tofa</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Birnin Magaji; Bungudu</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H80" t="n">
+        <v>0</v>
+      </c>
+      <c r="I80" t="n">
+        <v>0</v>
+      </c>
+      <c r="J80" t="n">
+        <v>0</v>
+      </c>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
+      <c r="O80" s="10" t="inlineStr"/>
+      <c r="P80" t="inlineStr"/>
+      <c r="Q80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Gusau</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Wanke</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Bungudu; Tsafe</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H81" t="n">
+        <v>0</v>
+      </c>
+      <c r="I81" t="n">
+        <v>0</v>
+      </c>
+      <c r="J81" t="n">
+        <v>0</v>
+      </c>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
+      <c r="O81" s="10" t="inlineStr"/>
+      <c r="P81" t="inlineStr"/>
+      <c r="Q81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Gusau</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Wonaka</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Birnin Magaji; Bungudu; Tsafe</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H82" t="n">
+        <v>0</v>
+      </c>
+      <c r="I82" t="n">
+        <v>0</v>
+      </c>
+      <c r="J82" t="n">
+        <v>0</v>
+      </c>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
+      <c r="O82" s="10" t="inlineStr"/>
+      <c r="P82" t="inlineStr"/>
+      <c r="Q82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Gusau</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Yandoton Daji</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Bungudu; Tsafe</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H83" t="n">
+        <v>0</v>
+      </c>
+      <c r="I83" t="n">
+        <v>0</v>
+      </c>
+      <c r="J83" t="n">
+        <v>0</v>
+      </c>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
+      <c r="O83" s="10" t="inlineStr"/>
+      <c r="P83" t="inlineStr"/>
+      <c r="Q83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Gusau</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Yankuzo B</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Tsafe</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H84" t="n">
+        <v>0</v>
+      </c>
+      <c r="I84" t="n">
+        <v>0</v>
+      </c>
+      <c r="J84" t="n">
+        <v>0</v>
+      </c>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
+      <c r="O84" s="10" t="inlineStr"/>
+      <c r="P84" t="inlineStr"/>
+      <c r="Q84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Gusau</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Yanware</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Tsafe</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H85" t="n">
+        <v>0</v>
+      </c>
+      <c r="I85" t="n">
+        <v>0</v>
+      </c>
+      <c r="J85" t="n">
+        <v>0</v>
+      </c>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr"/>
+      <c r="N85" t="inlineStr"/>
+      <c r="O85" s="10" t="inlineStr"/>
+      <c r="P85" t="inlineStr"/>
+      <c r="Q85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Maru</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Ruwan Doruma</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Bungudu</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H86" t="n">
+        <v>5</v>
+      </c>
+      <c r="I86" t="n">
+        <v>1</v>
+      </c>
+      <c r="J86" t="n">
+        <v>47</v>
+      </c>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr"/>
+      <c r="N86" t="inlineStr"/>
+      <c r="O86" s="10" t="inlineStr"/>
+      <c r="P86" t="inlineStr"/>
+      <c r="Q86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Maru</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Maru</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Bungudu; Maradun</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H87" t="n">
+        <v>9</v>
+      </c>
+      <c r="I87" t="n">
+        <v>1</v>
+      </c>
+      <c r="J87" t="n">
+        <v>26</v>
+      </c>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
+      <c r="O87" s="10" t="inlineStr"/>
+      <c r="P87" t="inlineStr"/>
+      <c r="Q87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Maru</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Mayanchi</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Talata Mafara</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H88" t="n">
+        <v>3</v>
+      </c>
+      <c r="I88" t="n">
+        <v>1</v>
+      </c>
+      <c r="J88" t="n">
+        <v>26</v>
+      </c>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr"/>
+      <c r="N88" t="inlineStr"/>
+      <c r="O88" s="10" t="inlineStr"/>
+      <c r="P88" t="inlineStr"/>
+      <c r="Q88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Maru</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Bena</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr"/>
+      <c r="G89" t="inlineStr"/>
+      <c r="H89" t="n">
+        <v>1</v>
+      </c>
+      <c r="I89" t="n">
+        <v>0</v>
+      </c>
+      <c r="J89" t="n">
+        <v>6</v>
+      </c>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr"/>
+      <c r="N89" t="inlineStr"/>
+      <c r="O89" s="10" t="inlineStr"/>
+      <c r="P89" t="inlineStr"/>
+      <c r="Q89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Maru</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Ayu</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr"/>
+      <c r="G90" t="inlineStr"/>
+      <c r="H90" t="n">
+        <v>0</v>
+      </c>
+      <c r="I90" t="n">
+        <v>0</v>
+      </c>
+      <c r="J90" t="n">
+        <v>0</v>
+      </c>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr"/>
+      <c r="N90" t="inlineStr"/>
+      <c r="O90" s="10" t="inlineStr"/>
+      <c r="P90" t="inlineStr"/>
+      <c r="Q90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Maru</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Bagega</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr"/>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Anka; Bukkuyum</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H91" t="n">
+        <v>0</v>
+      </c>
+      <c r="I91" t="n">
+        <v>0</v>
+      </c>
+      <c r="J91" t="n">
+        <v>0</v>
+      </c>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr"/>
+      <c r="N91" t="inlineStr"/>
+      <c r="O91" s="10" t="inlineStr"/>
+      <c r="P91" t="inlineStr"/>
+      <c r="Q91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Maru</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Bindin</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr"/>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Anka; Bungudu</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H92" t="n">
+        <v>0</v>
+      </c>
+      <c r="I92" t="n">
+        <v>0</v>
+      </c>
+      <c r="J92" t="n">
+        <v>0</v>
+      </c>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr"/>
+      <c r="N92" t="inlineStr"/>
+      <c r="O92" s="10" t="inlineStr"/>
+      <c r="P92" t="inlineStr"/>
+      <c r="Q92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Maru</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Bingi</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Bungudu</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H93" t="n">
+        <v>0</v>
+      </c>
+      <c r="I93" t="n">
+        <v>0</v>
+      </c>
+      <c r="J93" t="n">
+        <v>0</v>
+      </c>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr"/>
+      <c r="N93" t="inlineStr"/>
+      <c r="O93" s="10" t="inlineStr"/>
+      <c r="P93" t="inlineStr"/>
+      <c r="Q93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Maru</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Bingi North</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Bungudu; Gusau</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H94" t="n">
+        <v>0</v>
+      </c>
+      <c r="I94" t="n">
+        <v>0</v>
+      </c>
+      <c r="J94" t="n">
+        <v>0</v>
+      </c>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr"/>
+      <c r="N94" t="inlineStr"/>
+      <c r="O94" s="10" t="inlineStr"/>
+      <c r="P94" t="inlineStr"/>
+      <c r="Q94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Maru</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Bingi South</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Bungudu; Gusau</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H95" t="n">
+        <v>0</v>
+      </c>
+      <c r="I95" t="n">
+        <v>0</v>
+      </c>
+      <c r="J95" t="n">
+        <v>0</v>
+      </c>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
+      <c r="O95" s="10" t="inlineStr"/>
+      <c r="P95" t="inlineStr"/>
+      <c r="Q95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Maru</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Damaga Gamagiwa</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr"/>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Bungudu; Maradun</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H96" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" t="n">
+        <v>0</v>
+      </c>
+      <c r="J96" t="n">
+        <v>0</v>
+      </c>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr"/>
+      <c r="N96" t="inlineStr"/>
+      <c r="O96" s="10" t="inlineStr"/>
+      <c r="P96" t="inlineStr"/>
+      <c r="Q96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Maru</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Dan Umaru Mairairai</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr"/>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr"/>
+      <c r="G97" t="inlineStr"/>
+      <c r="H97" t="n">
+        <v>0</v>
+      </c>
+      <c r="I97" t="n">
+        <v>0</v>
+      </c>
+      <c r="J97" t="n">
+        <v>0</v>
+      </c>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr"/>
+      <c r="N97" t="inlineStr"/>
+      <c r="O97" s="10" t="inlineStr"/>
+      <c r="P97" t="inlineStr"/>
+      <c r="Q97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Maru</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Dangulbi</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr"/>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Anka; Bukkuyum</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H98" t="n">
+        <v>0</v>
+      </c>
+      <c r="I98" t="n">
+        <v>0</v>
+      </c>
+      <c r="J98" t="n">
+        <v>0</v>
+      </c>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr"/>
+      <c r="N98" t="inlineStr"/>
+      <c r="O98" s="10" t="inlineStr"/>
+      <c r="P98" t="inlineStr"/>
+      <c r="Q98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Maru</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Dankurmi</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr"/>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Anka; Bukkuyum</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H99" t="n">
+        <v>0</v>
+      </c>
+      <c r="I99" t="n">
+        <v>0</v>
+      </c>
+      <c r="J99" t="n">
+        <v>0</v>
+      </c>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr"/>
+      <c r="N99" t="inlineStr"/>
+      <c r="O99" s="10" t="inlineStr"/>
+      <c r="P99" t="inlineStr"/>
+      <c r="Q99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Maru</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Dansadau</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr"/>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Gusau; Tsafe</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H100" t="n">
+        <v>0</v>
+      </c>
+      <c r="I100" t="n">
+        <v>0</v>
+      </c>
+      <c r="J100" t="n">
+        <v>0</v>
+      </c>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr"/>
+      <c r="N100" t="inlineStr"/>
+      <c r="O100" s="10" t="inlineStr"/>
+      <c r="P100" t="inlineStr"/>
+      <c r="Q100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Maru</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Dosara Birnin Kaya</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr"/>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Maradun; Talata Mafara</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H101" t="n">
+        <v>0</v>
+      </c>
+      <c r="I101" t="n">
+        <v>0</v>
+      </c>
+      <c r="J101" t="n">
+        <v>0</v>
+      </c>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr"/>
+      <c r="N101" t="inlineStr"/>
+      <c r="O101" s="10" t="inlineStr"/>
+      <c r="P101" t="inlineStr"/>
+      <c r="Q101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Maru</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Gada Karakai</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr"/>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Bungudu; Maradun</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H102" t="n">
+        <v>0</v>
+      </c>
+      <c r="I102" t="n">
+        <v>0</v>
+      </c>
+      <c r="J102" t="n">
+        <v>0</v>
+      </c>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr"/>
+      <c r="N102" t="inlineStr"/>
+      <c r="O102" s="10" t="inlineStr"/>
+      <c r="P102" t="inlineStr"/>
+      <c r="Q102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Maru</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Gwaram</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr"/>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Anka; Talata Mafara</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H103" t="n">
+        <v>0</v>
+      </c>
+      <c r="I103" t="n">
+        <v>0</v>
+      </c>
+      <c r="J103" t="n">
+        <v>0</v>
+      </c>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" t="inlineStr"/>
+      <c r="N103" t="inlineStr"/>
+      <c r="O103" s="10" t="inlineStr"/>
+      <c r="P103" t="inlineStr"/>
+      <c r="Q103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Maru</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Gwashi</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr"/>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Anka; Bukkuyum</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H104" t="n">
+        <v>0</v>
+      </c>
+      <c r="I104" t="n">
+        <v>0</v>
+      </c>
+      <c r="J104" t="n">
+        <v>0</v>
+      </c>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" t="inlineStr"/>
+      <c r="N104" t="inlineStr"/>
+      <c r="O104" s="10" t="inlineStr"/>
+      <c r="P104" t="inlineStr"/>
+      <c r="Q104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Maru</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Kakangi</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr"/>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr"/>
+      <c r="G105" t="inlineStr"/>
+      <c r="H105" t="n">
+        <v>0</v>
+      </c>
+      <c r="I105" t="n">
+        <v>0</v>
+      </c>
+      <c r="J105" t="n">
+        <v>0</v>
+      </c>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" t="inlineStr"/>
+      <c r="N105" t="inlineStr"/>
+      <c r="O105" s="10" t="inlineStr"/>
+      <c r="P105" t="inlineStr"/>
+      <c r="Q105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Maru</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Kanoma</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr"/>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Anka; Bungudu; Talata Mafara</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H106" t="n">
+        <v>0</v>
+      </c>
+      <c r="I106" t="n">
+        <v>0</v>
+      </c>
+      <c r="J106" t="n">
+        <v>0</v>
+      </c>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" t="inlineStr"/>
+      <c r="N106" t="inlineStr"/>
+      <c r="O106" s="10" t="inlineStr"/>
+      <c r="P106" t="inlineStr"/>
+      <c r="Q106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Maru</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Kotonkoro</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr"/>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr"/>
+      <c r="G107" t="inlineStr"/>
+      <c r="H107" t="n">
+        <v>0</v>
+      </c>
+      <c r="I107" t="n">
+        <v>0</v>
+      </c>
+      <c r="J107" t="n">
+        <v>0</v>
+      </c>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" t="inlineStr"/>
+      <c r="N107" t="inlineStr"/>
+      <c r="O107" s="10" t="inlineStr"/>
+      <c r="P107" t="inlineStr"/>
+      <c r="Q107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Maru</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Kuyanbana</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr"/>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr"/>
+      <c r="G108" t="inlineStr"/>
+      <c r="H108" t="n">
+        <v>0</v>
+      </c>
+      <c r="I108" t="n">
+        <v>0</v>
+      </c>
+      <c r="J108" t="n">
+        <v>0</v>
+      </c>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" t="inlineStr"/>
+      <c r="N108" t="inlineStr"/>
+      <c r="O108" s="10" t="inlineStr"/>
+      <c r="P108" t="inlineStr"/>
+      <c r="Q108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Maru</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Kuyello</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr"/>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Gusau</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H109" t="n">
+        <v>0</v>
+      </c>
+      <c r="I109" t="n">
+        <v>0</v>
+      </c>
+      <c r="J109" t="n">
+        <v>0</v>
+      </c>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" t="inlineStr"/>
+      <c r="N109" t="inlineStr"/>
+      <c r="O109" s="10" t="inlineStr"/>
+      <c r="P109" t="inlineStr"/>
+      <c r="Q109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Maru</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Magajin Gari 2</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr"/>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr"/>
+      <c r="G110" t="inlineStr"/>
+      <c r="H110" t="n">
+        <v>0</v>
+      </c>
+      <c r="I110" t="n">
+        <v>0</v>
+      </c>
+      <c r="J110" t="n">
+        <v>0</v>
+      </c>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" t="inlineStr"/>
+      <c r="N110" t="inlineStr"/>
+      <c r="O110" s="10" t="inlineStr"/>
+      <c r="P110" t="inlineStr"/>
+      <c r="Q110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Maru</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Magajin Gari 3</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr"/>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr"/>
+      <c r="G111" t="inlineStr"/>
+      <c r="H111" t="n">
+        <v>0</v>
+      </c>
+      <c r="I111" t="n">
+        <v>0</v>
+      </c>
+      <c r="J111" t="n">
+        <v>0</v>
+      </c>
+      <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" t="inlineStr"/>
+      <c r="N111" t="inlineStr"/>
+      <c r="O111" s="10" t="inlineStr"/>
+      <c r="P111" t="inlineStr"/>
+      <c r="Q111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Maru</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Magami</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr"/>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Bungudu; Gusau; Tsafe</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H112" t="n">
+        <v>0</v>
+      </c>
+      <c r="I112" t="n">
+        <v>0</v>
+      </c>
+      <c r="J112" t="n">
+        <v>0</v>
+      </c>
+      <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" t="inlineStr"/>
+      <c r="N112" t="inlineStr"/>
+      <c r="O112" s="10" t="inlineStr"/>
+      <c r="P112" t="inlineStr"/>
+      <c r="Q112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Maru</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Morai</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr"/>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Maradun; Talata Mafara</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H113" t="n">
+        <v>0</v>
+      </c>
+      <c r="I113" t="n">
+        <v>0</v>
+      </c>
+      <c r="J113" t="n">
+        <v>0</v>
+      </c>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" t="inlineStr"/>
+      <c r="N113" t="inlineStr"/>
+      <c r="O113" s="10" t="inlineStr"/>
+      <c r="P113" t="inlineStr"/>
+      <c r="Q113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Maru</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Sabon Birni</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr"/>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Anka</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H114" t="n">
+        <v>0</v>
+      </c>
+      <c r="I114" t="n">
+        <v>0</v>
+      </c>
+      <c r="J114" t="n">
+        <v>0</v>
+      </c>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" t="inlineStr"/>
+      <c r="N114" t="inlineStr"/>
+      <c r="O114" s="10" t="inlineStr"/>
+      <c r="P114" t="inlineStr"/>
+      <c r="Q114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Maru</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Wasagu</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr"/>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr"/>
+      <c r="G115" t="inlineStr"/>
+      <c r="H115" t="n">
+        <v>0</v>
+      </c>
+      <c r="I115" t="n">
+        <v>0</v>
+      </c>
+      <c r="J115" t="n">
+        <v>0</v>
+      </c>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" t="inlineStr"/>
+      <c r="N115" t="inlineStr"/>
+      <c r="O115" s="10" t="inlineStr"/>
+      <c r="P115" t="inlineStr"/>
+      <c r="Q115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Maru</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Wuya</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr"/>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Anka</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H116" t="n">
+        <v>0</v>
+      </c>
+      <c r="I116" t="n">
+        <v>0</v>
+      </c>
+      <c r="J116" t="n">
+        <v>0</v>
+      </c>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" t="inlineStr"/>
+      <c r="N116" t="inlineStr"/>
+      <c r="O116" s="10" t="inlineStr"/>
+      <c r="P116" t="inlineStr"/>
+      <c r="Q116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Maru</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Yarsabaya</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr"/>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Anka; Talata Mafara</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H117" t="n">
+        <v>0</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0</v>
+      </c>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" t="inlineStr"/>
+      <c r="N117" t="inlineStr"/>
+      <c r="O117" s="10" t="inlineStr"/>
+      <c r="P117" t="inlineStr"/>
+      <c r="Q117" t="inlineStr"/>
+    </row>
   </sheetData>
   <dataValidations count="5">
-    <dataValidation sqref="K2:K52" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="K2:K117" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation sqref="L2:L52" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="L2:L117" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"N/A - fully accessible,Insecurity / conflict,Physical access (terrain, flooding, roads),Population absent / relocated,Building-footprint issue (no eligible structures),Access denied by authorities / community,Other"</formula1>
     </dataValidation>
-    <dataValidation sqref="P2:P52" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="P2:P117" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Partner,IMPACT (default - accessible until reported otherwise)"</formula1>
     </dataValidation>
-    <dataValidation sqref="Q2:Q52" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="Q2:Q117" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Partner's own template,Email,WhatsApp/verbal (coordinator-transcribed),Point-level file annotation,N/A"</formula1>
     </dataValidation>
-    <dataValidation sqref="O2:O52" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid date" error="Enter an actual date between 01 Jul 2026 and today - click the cell and use the date picker, or type e.g. 27-Aug-2026. Free text and out-of-range dates (including future dates) are rejected here so they don't need to be caught and excluded later." type="date" operator="between">
+    <dataValidation sqref="O2:O117" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid date" error="Enter an actual date between 01 Jul 2026 and today - click the cell and use the date picker, or type e.g. 27-Aug-2026. Free text and out-of-range dates (including future dates) are rejected here so they don't need to be caught and excluded later." type="date" operator="between">
       <formula1>2026-07-01</formula1>
-      <formula2>2026-08-28</formula2>
+      <formula2>2026-09-20</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3167,7 +6388,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O84"/>
+  <dimension ref="A1:O77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3277,7 +6498,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Kalizoram</t>
+          <t>Magumeri</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -3287,7 +6508,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>idp_NG008020_1</t>
+          <t>idp_NG008020_3</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -3297,12 +6518,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>42</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>42</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -3326,7 +6547,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Gajiganna</t>
+          <t>Magumeri</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -3336,7 +6557,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>idp_NG008020_10</t>
+          <t>idp_NG008020_supp1</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -3346,12 +6567,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -3385,7 +6606,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>idp_NG008020_3</t>
+          <t>idp_NG008020_supp2</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -3395,12 +6616,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -3424,20 +6645,24 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Kalizoram</t>
+          <t>Magumeri</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>non_idp_NG008020_1</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr"/>
+          <t>idp_NG008020_supp3</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
       <c r="G5" t="inlineStr">
         <is>
           <t>6</t>
@@ -3474,15 +6699,19 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>non_idp_NG008020_10</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
+          <t>idp_NG008020_supp4</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
       <c r="G6" t="inlineStr">
         <is>
           <t>6</t>
@@ -3514,20 +6743,24 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Kalizoram</t>
+          <t>Magumeri</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>non_idp_NG008020_11</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr"/>
+          <t>idp_NG008020_supp5</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
       <c r="G7" t="inlineStr">
         <is>
           <t>6</t>
@@ -3559,20 +6792,24 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Titiwa</t>
+          <t>Magumeri</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>non_idp_NG008020_12</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr"/>
+          <t>idp_NG008020_supp6</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>In-camp</t>
+        </is>
+      </c>
       <c r="G8" t="inlineStr">
         <is>
           <t>6</t>
@@ -3604,20 +6841,24 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Titiwa</t>
+          <t>Magumeri</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>non_idp_NG008020_13</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr"/>
+          <t>idp_NG008020_supp7</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>In-camp</t>
+        </is>
+      </c>
       <c r="G9" t="inlineStr">
         <is>
           <t>6</t>
@@ -3649,7 +6890,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Titiwa</t>
+          <t>Magumeri</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -3659,7 +6900,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>non_idp_NG008020_14</t>
+          <t>non_idp_NG008020_10</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
@@ -3694,7 +6935,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Gajiganna</t>
+          <t>Magumeri</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -3704,7 +6945,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>non_idp_NG008020_15</t>
+          <t>non_idp_NG008020_7</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
@@ -3739,7 +6980,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ngulabamma</t>
+          <t>Magumeri</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -3749,7 +6990,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>non_idp_NG008020_16</t>
+          <t>non_idp_NG008020_9</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
@@ -3784,7 +7025,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ngulabamma</t>
+          <t>Kareram</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -3794,7 +7035,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>non_idp_NG008020_17</t>
+          <t>non_idp_NG008020_supp1</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
@@ -3829,7 +7070,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ngulabamma</t>
+          <t>Ardoram</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3839,7 +7080,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>non_idp_NG008020_2</t>
+          <t>non_idp_NG008020_supp10</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
@@ -3874,7 +7115,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Kupti</t>
+          <t>Magumeri</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3884,7 +7125,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>non_idp_NG008020_3</t>
+          <t>non_idp_NG008020_supp12</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
@@ -3919,7 +7160,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Borno Yesu</t>
+          <t>Hoyo Chingua</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3929,7 +7170,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>non_idp_NG008020_4</t>
+          <t>non_idp_NG008020_supp13</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
@@ -3964,7 +7205,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ngamma</t>
+          <t>Ardoram</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3974,7 +7215,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>non_idp_NG008020_5</t>
+          <t>non_idp_NG008020_supp14</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
@@ -4009,7 +7250,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ngamma</t>
+          <t>Gubio 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -4019,7 +7260,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>non_idp_NG008020_6</t>
+          <t>non_idp_NG008020_supp17</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
@@ -4054,7 +7295,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Magumeri</t>
+          <t>Kareram</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4064,7 +7305,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>non_idp_NG008020_7</t>
+          <t>non_idp_NG008020_supp18</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
@@ -4099,7 +7340,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Furram</t>
+          <t>Hoyo Chingua</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4109,7 +7350,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>non_idp_NG008020_8</t>
+          <t>non_idp_NG008020_supp3</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
@@ -4144,7 +7385,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Magumeri</t>
+          <t>Ardoram</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4154,7 +7395,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>non_idp_NG008020_9</t>
+          <t>non_idp_NG008020_supp4</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
@@ -4184,37 +7425,33 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Maiduguri</t>
+          <t>Magumeri</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Bolori 1</t>
+          <t>Hoyo Chingua</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>IDP</t>
+          <t>Non-IDP</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>idp_NG008021_1</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>In-host</t>
-        </is>
-      </c>
+          <t>non_idp_NG008020_supp5</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -4233,37 +7470,33 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Maiduguri</t>
+          <t>Magumeri</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Maisandari</t>
+          <t>Gubio 1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>IDP</t>
+          <t>Non-IDP</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>idp_NG008021_10</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>In-host</t>
-        </is>
-      </c>
+          <t>non_idp_NG008020_supp6</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -4282,37 +7515,33 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Maiduguri</t>
+          <t>Magumeri</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Bolori 2</t>
+          <t>Hoyo Chingua</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>IDP</t>
+          <t>Non-IDP</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>idp_NG008021_13</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>In-host</t>
-        </is>
-      </c>
+          <t>non_idp_NG008020_supp7</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -4336,7 +7565,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Maisandari</t>
+          <t>Bolori 1</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4346,7 +7575,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>idp_NG008021_3</t>
+          <t>idp_NG008021_1</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -4385,7 +7614,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Bolori 2</t>
+          <t>Maisandari</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4395,7 +7624,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>idp_NG008021_5</t>
+          <t>idp_NG008021_10</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -4405,12 +7634,12 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>18</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -4434,7 +7663,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Gwange 3</t>
+          <t>Bolori 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4444,7 +7673,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>idp_NG008021_7</t>
+          <t>idp_NG008021_13</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -4454,12 +7683,12 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>30</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -4483,7 +7712,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Bolori 1</t>
+          <t>Maisandari</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4493,7 +7722,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>idp_NG008021_9</t>
+          <t>idp_NG008021_3</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -4503,12 +7732,12 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -4532,28 +7761,32 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Maisandari</t>
+          <t>Bolori 2</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>non_idp_NG008021_1</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr"/>
+          <t>idp_NG008021_5</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -4582,23 +7815,27 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>non_idp_NG008021_12</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr"/>
+          <t>idp_NG008021_7</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4622,20 +7859,24 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Yajiwa</t>
+          <t>Bolori 1</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>non_idp_NG008021_13</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr"/>
+          <t>idp_NG008021_9</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
       <c r="G31" t="inlineStr">
         <is>
           <t>6</t>
@@ -4677,18 +7918,18 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>non_idp_NG008021_14</t>
+          <t>non_idp_NG008021_1</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4712,7 +7953,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Bolori 2</t>
+          <t>Gwange 3</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4722,18 +7963,18 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>non_idp_NG008021_16</t>
+          <t>non_idp_NG008021_12</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4757,7 +7998,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Bolori 1</t>
+          <t>Yajiwa</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4767,18 +8008,18 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>non_idp_NG008021_2</t>
+          <t>non_idp_NG008021_13</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4812,18 +8053,18 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>non_idp_NG008021_5</t>
+          <t>non_idp_NG008021_14</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4847,7 +8088,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Bolori 2</t>
+          <t>Bolori 1</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4857,18 +8098,18 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>non_idp_NG008021_8</t>
+          <t>non_idp_NG008021_16</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4892,7 +8133,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Gwange 2</t>
+          <t>Mafoni</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4902,7 +8143,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>non_idp_NG008021_9</t>
+          <t>non_idp_NG008021_2</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
@@ -4927,42 +8168,38 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Zamfara</t>
+          <t>Borno</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Gusau</t>
+          <t>Maiduguri</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Tudun Wada</t>
+          <t>Maisandari</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>IDP</t>
+          <t>Non-IDP</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>idp_NG037007_1</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>In-host</t>
-        </is>
-      </c>
+          <t>non_idp_NG008021_5</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>18</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4976,42 +8213,38 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Zamfara</t>
+          <t>Borno</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Gusau</t>
+          <t>Maiduguri</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Galadima</t>
+          <t>Bolori 2</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>IDP</t>
+          <t>Non-IDP</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>idp_NG037007_11</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>In-host</t>
-        </is>
-      </c>
+          <t>non_idp_NG008021_8</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5025,42 +8258,38 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Zamfara</t>
+          <t>Borno</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Gusau</t>
+          <t>Maiduguri</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Tudun Wada</t>
+          <t>Maisandari</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>IDP</t>
+          <t>Non-IDP</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>idp_NG037007_13</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>In-host</t>
-        </is>
-      </c>
+          <t>non_idp_NG008021_9</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>18</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5084,7 +8313,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Galadima</t>
+          <t>Tudun Wada</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5094,7 +8323,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>idp_NG037007_14</t>
+          <t>idp_NG037007_1</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -5104,12 +8333,12 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5133,7 +8362,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Tudun Wada</t>
+          <t>Galadima</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5143,7 +8372,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>idp_NG037007_17</t>
+          <t>idp_NG037007_11</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -5153,12 +8382,12 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5182,7 +8411,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Mada</t>
+          <t>Tudun Wada</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5192,22 +8421,22 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>idp_NG037007_2</t>
+          <t>idp_NG037007_13</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>In-camp</t>
+          <t>In-host</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5231,7 +8460,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Wanke</t>
+          <t>Galadima</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5241,7 +8470,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>idp_NG037007_4</t>
+          <t>idp_NG037007_14</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -5251,12 +8480,12 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>24</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5280,7 +8509,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Magami</t>
+          <t>Tudun Wada</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5290,7 +8519,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>idp_NG037007_5</t>
+          <t>idp_NG037007_17</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -5329,7 +8558,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Wanke</t>
+          <t>Galadima</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5339,7 +8568,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>idp_NG037007_6</t>
+          <t>idp_NG037007_8</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -5349,12 +8578,12 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>24</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5378,7 +8607,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Wanke</t>
+          <t>Galadima</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5388,7 +8617,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>idp_NG037007_7</t>
+          <t>idp_NG037007_supp1</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -5427,7 +8656,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Galadima</t>
+          <t>Mayana</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -5437,7 +8666,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>idp_NG037007_8</t>
+          <t>idp_NG037007_supp2</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -5447,12 +8676,12 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5476,20 +8705,24 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Tudun Wada</t>
+          <t>Galadima</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>non_idp_NG037007_1</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr"/>
+          <t>idp_NG037007_supp4</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
       <c r="G49" t="inlineStr">
         <is>
           <t>6</t>
@@ -5521,7 +8754,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Rijiya</t>
+          <t>Tudun Wada</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -5531,7 +8764,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>non_idp_NG037007_13</t>
+          <t>non_idp_NG037007_1</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
@@ -5566,7 +8799,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Tudun Wada</t>
+          <t>Galadima</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -5656,7 +8889,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Wonaka</t>
+          <t>Furfuri Kwaikwai</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -5666,7 +8899,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>non_idp_NG037007_2</t>
+          <t>non_idp_NG037007_4</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
@@ -5701,7 +8934,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Ruwan Bore</t>
+          <t>Madawaki</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -5711,18 +8944,18 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>non_idp_NG037007_3</t>
+          <t>non_idp_NG037007_6</t>
         </is>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5746,7 +8979,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Furfuri Kwaikwai</t>
+          <t>Mayana</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -5756,18 +8989,18 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>non_idp_NG037007_4</t>
+          <t>non_idp_NG037007_9</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>24</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5791,7 +9024,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Magami</t>
+          <t>Tudun Wada</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -5801,7 +9034,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>non_idp_NG037007_5</t>
+          <t>non_idp_NG037007_supp3</t>
         </is>
       </c>
       <c r="F56" t="inlineStr"/>
@@ -5846,18 +9079,18 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>non_idp_NG037007_6</t>
+          <t>non_idp_NG037007_supp4</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -5881,7 +9114,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Wanke</t>
+          <t>Tudun Wada</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -5891,7 +9124,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>non_idp_NG037007_8</t>
+          <t>non_idp_NG037007_supp5</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
@@ -5926,7 +9159,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Tudun Wada</t>
+          <t>Mayana</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -5936,18 +9169,18 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>non_idp_NG037007_9</t>
+          <t>non_idp_NG037007_supp6</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6040,12 +9273,12 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>30</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6089,12 +9322,12 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>30</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6118,24 +9351,20 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Dangulbi</t>
+          <t>Ruwan Doruma</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>IDP</t>
+          <t>Non-IDP</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>idp_NG037010_3</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>In-camp</t>
-        </is>
-      </c>
+          <t>non_idp_NG037010_17</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
           <t>6</t>
@@ -6167,32 +9396,28 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Kanoma</t>
+          <t>Maru</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>IDP</t>
+          <t>Non-IDP</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>idp_NG037010_4</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>In-host</t>
-        </is>
-      </c>
+          <t>non_idp_NG037010_supp11</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6216,24 +9441,20 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Kanoma</t>
+          <t>Maru</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>IDP</t>
+          <t>Non-IDP</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>idp_NG037010_8</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>In-host</t>
-        </is>
-      </c>
+          <t>non_idp_NG037010_supp12</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
           <t>6</t>
@@ -6265,32 +9486,28 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Bindin</t>
+          <t>Mayanchi</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>IDP</t>
+          <t>Non-IDP</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>idp_NG037010_9</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>In-host</t>
-        </is>
-      </c>
+          <t>non_idp_NG037010_supp15</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6314,7 +9531,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Kuyanbana</t>
+          <t>Mayanchi</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -6324,7 +9541,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>non_idp_NG037010_1</t>
+          <t>non_idp_NG037010_supp18</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
@@ -6359,7 +9576,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Kuyanbana</t>
+          <t>Maru</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -6369,7 +9586,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>non_idp_NG037010_10</t>
+          <t>non_idp_NG037010_supp19</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
@@ -6404,7 +9621,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Bingi</t>
+          <t>Maru</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -6414,7 +9631,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>non_idp_NG037010_11</t>
+          <t>non_idp_NG037010_supp2</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
@@ -6449,7 +9666,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Kuyanbana</t>
+          <t>Maru</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -6459,7 +9676,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>non_idp_NG037010_12</t>
+          <t>non_idp_NG037010_supp21</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
@@ -6494,7 +9711,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Dansadau</t>
+          <t>Ruwan Doruma</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -6504,7 +9721,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>non_idp_NG037010_13</t>
+          <t>non_idp_NG037010_supp25</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
@@ -6539,7 +9756,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Dansadau</t>
+          <t>Ruwan Doruma</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -6549,7 +9766,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>non_idp_NG037010_14</t>
+          <t>non_idp_NG037010_supp26</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
@@ -6584,7 +9801,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Dansadau</t>
+          <t>Bena</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -6594,7 +9811,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>non_idp_NG037010_15</t>
+          <t>non_idp_NG037010_supp27</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
@@ -6629,7 +9846,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Dankurmi</t>
+          <t>Mayanchi</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -6639,7 +9856,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>non_idp_NG037010_16</t>
+          <t>non_idp_NG037010_supp28</t>
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
@@ -6674,7 +9891,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Ruwan Doruma</t>
+          <t>Maru</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -6684,7 +9901,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>non_idp_NG037010_17</t>
+          <t>non_idp_NG037010_supp3</t>
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
@@ -6719,7 +9936,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Dankurmi</t>
+          <t>Ruwan Doruma</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -6729,7 +9946,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>non_idp_NG037010_2</t>
+          <t>non_idp_NG037010_supp4</t>
         </is>
       </c>
       <c r="F76" t="inlineStr"/>
@@ -6764,7 +9981,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Kuyanbana</t>
+          <t>Maru</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -6774,7 +9991,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>non_idp_NG037010_3</t>
+          <t>non_idp_NG037010_supp6</t>
         </is>
       </c>
       <c r="F77" t="inlineStr"/>
@@ -6796,338 +10013,23 @@
       <c r="N77" t="inlineStr"/>
       <c r="O77" t="inlineStr"/>
     </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>Zamfara</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Maru</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Kanoma</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>Non-IDP</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>non_idp_NG037010_4</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr"/>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" s="10" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
-      <c r="O78" t="inlineStr"/>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>Zamfara</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Maru</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Dangulbi</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>Non-IDP</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>non_idp_NG037010_5</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr"/>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" s="10" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
-      <c r="O79" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>Zamfara</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Maru</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Bindin</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>Non-IDP</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>non_idp_NG037010_6</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr"/>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" s="10" t="inlineStr"/>
-      <c r="N80" t="inlineStr"/>
-      <c r="O80" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>Zamfara</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Maru</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Bingi</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>Non-IDP</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>non_idp_NG037010_7</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr"/>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" s="10" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
-      <c r="O81" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>Zamfara</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Maru</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Kuyanbana</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>Non-IDP</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>non_idp_NG037010_8</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr"/>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" s="10" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
-      <c r="O82" t="inlineStr"/>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Zamfara</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Maru</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Dansadau</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>Non-IDP</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>non_idp_NG037010_9</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr"/>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" s="10" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
-      <c r="O83" t="inlineStr"/>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Zamfara</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>Maru</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Dangulbi</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>Non-IDP</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>non_idp_NG037010_supp1</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr"/>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" s="10" t="inlineStr"/>
-      <c r="N84" t="inlineStr"/>
-      <c r="O84" t="inlineStr"/>
-    </row>
   </sheetData>
   <dataValidations count="5">
-    <dataValidation sqref="I2:I84" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I2:I77" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation sqref="J2:J84" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J2:J77" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"N/A - fully accessible,Insecurity / conflict,Physical access (terrain, flooding, roads),Population absent / relocated,Building-footprint issue (no eligible structures),Access denied by authorities / community,Other"</formula1>
     </dataValidation>
-    <dataValidation sqref="N2:N84" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="N2:N77" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Partner,IMPACT (default - accessible until reported otherwise)"</formula1>
     </dataValidation>
-    <dataValidation sqref="O2:O84" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="O2:O77" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Partner's own template,Email,WhatsApp/verbal (coordinator-transcribed),Point-level file annotation,N/A"</formula1>
     </dataValidation>
-    <dataValidation sqref="M2:M84" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid date" error="Enter an actual date between 01 Jul 2026 and today - click the cell and use the date picker, or type e.g. 27-Aug-2026. Free text and out-of-range dates (including future dates) are rejected here so they don't need to be caught and excluded later." type="date" operator="between">
+    <dataValidation sqref="M2:M77" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid date" error="Enter an actual date between 01 Jul 2026 and today - click the cell and use the date picker, or type e.g. 27-Aug-2026. Free text and out-of-range dates (including future dates) are rejected here so they don't need to be caught and excluded later." type="date" operator="between">
       <formula1>2026-07-01</formula1>
-      <formula2>2026-08-28</formula2>
+      <formula2>2026-09-20</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7393,13 +10295,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B18C7B20-9B79-4A90-868A-9FCD8BB42671}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CFE27A73-B6E5-4420-A570-7D68432808DC}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1D1A3E94-F29E-4061-B496-3018FEE232FC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D56A8D02-B362-4C12-A0AB-7D97BFDF7F56}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C4CDFF4A-DD79-42D8-B113-E2814AC43109}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2221AB51-CA71-4DA6-A300-54039FF6D688}"/>
 </file>
--- a/resampling/input/accessibility_reports_generated/INTERSOS_accessibility_report.xlsx
+++ b/resampling/input/accessibility_reports_generated/INTERSOS_accessibility_report.xlsx
@@ -210,24 +210,25 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="ClusterAccessibility" displayName="ClusterAccessibility" ref="A1:O77" headerRowCount="1">
-  <autoFilter ref="A1:O77"/>
-  <tableColumns count="15">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="ClusterAccessibility" displayName="ClusterAccessibility" ref="A1:P90" headerRowCount="1">
+  <autoFilter ref="A1:P90"/>
+  <tableColumns count="16">
     <tableColumn id="1" name="State"/>
     <tableColumn id="2" name="LGA"/>
     <tableColumn id="3" name="Ward (GRID3)"/>
     <tableColumn id="4" name="Pop Type"/>
     <tableColumn id="5" name="Cluster ID"/>
-    <tableColumn id="6" name="IDP Category"/>
-    <tableColumn id="7" name="Target HHs (primary)"/>
-    <tableColumn id="8" name="Reserve HHs"/>
-    <tableColumn id="9" name="Accessible (Y/N)"/>
-    <tableColumn id="10" name="Reason category"/>
-    <tableColumn id="11" name="Reason notes"/>
-    <tableColumn id="12" name="% of target achieved so far"/>
-    <tableColumn id="13" name="Date reported"/>
-    <tableColumn id="14" name="Reported by (Partner / IMPACT-default)"/>
-    <tableColumn id="15" name="Source channel"/>
+    <tableColumn id="6" name="Status"/>
+    <tableColumn id="7" name="IDP Category"/>
+    <tableColumn id="8" name="Target HHs (primary)"/>
+    <tableColumn id="9" name="Reserve HHs"/>
+    <tableColumn id="10" name="Accessible (Y/N)"/>
+    <tableColumn id="11" name="Reason category"/>
+    <tableColumn id="12" name="Reason notes"/>
+    <tableColumn id="13" name="% of target achieved so far"/>
+    <tableColumn id="14" name="Date reported"/>
+    <tableColumn id="15" name="Reported by (Partner / IMPACT-default)"/>
+    <tableColumn id="16" name="Source channel"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
 </table>
@@ -522,7 +523,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -553,7 +554,7 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Assigned to you: 116 wards, 76 clusters</t>
+          <t>Assigned to you: 116 wards, 89 clusters</t>
         </is>
       </c>
     </row>
@@ -580,7 +581,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>A row with a very small Total target HHs figure (1-2) usually means a border case - GRID3 and OCHA/COD boundaries don't always agree exactly, so a small part of one of your clusters can fall just inside a ward you don't otherwise work in. This is expected, not an error - please still report on it like any other row if it's genuinely inaccessible. If a row also shows 'Yes' under 'Ward spans multiple LGAs', see that row's Note for what part of the ward is actually yours to report on.</t>
+          <t>If you've reported on a row before, your last answer is already shown here (Accessible/Reason/Date reported etc.) rather than a blank cell - please review it and only change it if something has actually changed since you last told us, don't assume a filled-in row is a mistake. On the 'Cluster Accessibility' sheet, a cluster you previously flagged that's since been removed from your assigned list entirely still appears, marked 'No longer in frame' in the Status column - kept so your earlier report isn't lost, but it's no longer something we need action on.</t>
         </is>
       </c>
     </row>
@@ -590,7 +591,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>For each ward, set Accessible (Y/N). Leave a ward's row otherwise blank if there's no issue there.</t>
+          <t>A row with a very small Total target HHs figure (1-2) usually means a border case - GRID3 and OCHA/COD boundaries don't always agree exactly, so a small part of one of your clusters can fall just inside a ward you don't otherwise work in. This is expected, not an error - please still report on it like any other row if it's genuinely inaccessible. If a row also shows 'Yes' under 'Ward spans multiple LGAs', see that row's Note for what part of the ward is actually yours to report on.</t>
         </is>
       </c>
     </row>
@@ -600,7 +601,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>For any ward marked 'No', pick the closest-fitting Reason category from the dropdown (use 'Other' plus a note if none fit), and add specific Reason notes - e.g. 'active clashes reported near [location] in the past week' is far more useful to us than just 'insecure'.</t>
+          <t>For each ward, set Accessible (Y/N). Leave a ward's row otherwise blank if there's no issue there.</t>
         </is>
       </c>
     </row>
@@ -610,7 +611,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>If you know it, fill in roughly what % of the target sample you were able to achieve in that ward before stopping - even a rough estimate helps, and please don't leave this blank if the true answer is 0%.</t>
+          <t>For any ward marked 'No', pick the closest-fitting Reason category from the dropdown (use 'Other' plus a note if none fit), and add specific Reason notes - e.g. 'active clashes reported near [location] in the past week' is far more useful to us than just 'insecure'.</t>
         </is>
       </c>
     </row>
@@ -620,7 +621,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>The last two columns ('Reported by' and 'Source channel') are for our own internal record-keeping - please leave them blank unless we've asked you to fill in a specific row on our behalf (e.g. transcribing a WhatsApp/verbal report into this sheet).</t>
+          <t>If you know it, fill in roughly what % of the target sample you were able to achieve in that ward before stopping - even a rough estimate helps, and please don't leave this blank if the true answer is 0%.</t>
         </is>
       </c>
     </row>
@@ -630,7 +631,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Only use the 'Cluster Accessibility' sheet (second tab) for a problem specific to ONE site/HH within an otherwise-fine ward - and only once you've already worked through that cluster's reserve/replacement households and they weren't enough to cover it. Don't use this sheet before exhausting your reserve list for that cluster, and don't use it as a second way to report the same ward-wide issue already captured on the first sheet.</t>
+          <t>The last two columns ('Reported by' and 'Source channel') are for our own internal record-keeping - please leave them blank unless we've asked you to fill in a specific row on our behalf (e.g. transcribing a WhatsApp/verbal report into this sheet).</t>
         </is>
       </c>
     </row>
@@ -640,58 +641,68 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Date reported must be an actual date, not typed text - click the cell and use Excel's date picker, or type it as e.g. 27-Aug-2026. The cell will reject anything that isn't a real date, or a date before 01 Jul 2026/after today.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="90" customHeight="1">
+          <t>Only use the 'Cluster Accessibility' sheet (second tab) for a problem specific to ONE site/HH within an otherwise-fine ward - and only once you've already worked through that cluster's reserve/replacement households and they weren't enough to cover it. Don't use this sheet before exhausting your reserve list for that cluster, and don't use it as a second way to report the same ward-wide issue already captured on the first sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="60" customHeight="1">
       <c r="A17" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="B17" s="6" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Date reported must be an actual date, not typed text - click the cell and use Excel's date picker, or type it as e.g. 27-Aug-2026. The cell will reject anything that isn't a real date, or a date before 01 Jul 2026/after today.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="90" customHeight="1">
+      <c r="A18" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
         <is>
           <t>IMPORTANT: please review your ENTIRE coverage area in one pass before sending this back to us, rather than reporting a few wards now and more later - this significantly cuts down the back-and-forth rounds we need with you. If genuinely new information comes in afterwards, send an updated copy of the FULL sheet (not just the changed rows) with a new Date reported - we track changes over time by date, so we don't need you to tell us what changed, just the current full picture.</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>Which sheet do I use?</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="7" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
         <is>
           <t>Sheet</t>
         </is>
       </c>
-      <c r="B20" s="7" t="inlineStr">
+      <c r="B21" s="7" t="inlineStr">
         <is>
           <t>Use for</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="45" customHeight="1">
-      <c r="A21" s="8" t="inlineStr">
-        <is>
-          <t>Ward Accessibility</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>Your main report. Use for any access problem affecting a ward generally - insecurity, flooding/terrain, population displacement, denied access, etc.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="45" customHeight="1">
       <c r="A22" s="8" t="inlineStr">
         <is>
+          <t>Ward Accessibility</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Your main report. Use for any access problem affecting a ward generally - insecurity, flooding/terrain, population displacement, denied access, etc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="45" customHeight="1">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
           <t>Cluster Accessibility</t>
         </is>
       </c>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>Secondary/detail only. Use ONLY for a problem specific to one site/HH, not the surrounding ward, and only after that cluster's reserve/replacement households were already used and weren't enough.</t>
         </is>
@@ -2063,12 +2074,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Maisandari</t>
+          <t>Bolori 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Maisandari</t>
+          <t>Bolori II</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2087,13 +2098,13 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I28" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J28" t="n">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
@@ -2116,12 +2127,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Bolori 2</t>
+          <t>Bolori 1</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Bolori II</t>
+          <t>Bolori I</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2131,7 +2142,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Jere</t>
+          <t>Konduga</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2140,13 +2151,13 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I29" t="n">
         <v>2</v>
       </c>
       <c r="J29" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
@@ -2169,12 +2180,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Bolori 1</t>
+          <t>Maisandari</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Bolori I</t>
+          <t>Maisandari</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2184,7 +2195,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Konduga</t>
+          <t>Jere</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2193,13 +2204,13 @@
         </is>
       </c>
       <c r="H30" t="n">
+        <v>6</v>
+      </c>
+      <c r="I30" t="n">
         <v>3</v>
       </c>
-      <c r="I30" t="n">
-        <v>2</v>
-      </c>
       <c r="J30" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
@@ -2241,10 +2252,10 @@
         <v>1</v>
       </c>
       <c r="I31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J31" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
@@ -2267,12 +2278,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Bulabulin</t>
+          <t>Gongolong</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Bulabulin</t>
+          <t>Bolori II</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2282,7 +2293,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gwoza</t>
+          <t>Jere</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2297,7 +2308,7 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
@@ -2320,21 +2331,29 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Fezzan</t>
+          <t>Auno</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Fezzan</t>
+          <t>Bolori I</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Jere; Konduga; Magumeri</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H33" t="n">
         <v>1</v>
       </c>
@@ -2365,12 +2384,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Lamisula</t>
+          <t>Bulabulin</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Lamisula</t>
+          <t>Bulabulin</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2380,7 +2399,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Jere</t>
+          <t>Gwoza</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2389,7 +2408,7 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I34" t="n">
         <v>0</v>
@@ -2418,29 +2437,21 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Limanti</t>
+          <t>Fezzan</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Limanti</t>
+          <t>Fezzan</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Bayo; Jere; Mafa</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
       <c r="H35" t="n">
         <v>1</v>
       </c>
@@ -2471,12 +2482,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Yajiwa</t>
+          <t>Lamisula</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Bolori I</t>
+          <t>Lamisula</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2486,7 +2497,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Jere; Konduga</t>
+          <t>Jere</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2495,7 +2506,7 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I36" t="n">
         <v>0</v>
@@ -2524,10 +2535,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Auno</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr"/>
+          <t>Limanti</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Limanti</t>
+        </is>
+      </c>
       <c r="E37" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -2535,7 +2550,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Jere; Konduga; Magumeri</t>
+          <t>Bayo; Jere; Mafa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2544,13 +2559,13 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I37" t="n">
         <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
@@ -2573,12 +2588,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Dala</t>
+          <t>Yajiwa</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Maisandari</t>
+          <t>Bolori I</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2603,7 +2618,7 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
@@ -2626,7 +2641,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Galtimari</t>
+          <t>Dala</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2641,7 +2656,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Jere</t>
+          <t>Jere; Konduga</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2650,7 +2665,7 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I39" t="n">
         <v>0</v>
@@ -2679,12 +2694,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Gamboru</t>
+          <t>Galtimari</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Gamboru</t>
+          <t>Maisandari</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2703,7 +2718,7 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I40" t="n">
         <v>0</v>
@@ -2732,10 +2747,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Gomari</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr"/>
+          <t>Gamboru</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Gamboru</t>
+        </is>
+      </c>
       <c r="E41" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -2743,7 +2762,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Jere; Konduga</t>
+          <t>Jere</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2752,7 +2771,7 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
@@ -2781,7 +2800,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Gongolong</t>
+          <t>Gomari</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
@@ -2792,7 +2811,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Jere</t>
+          <t>Jere; Konduga</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -3312,7 +3331,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Galadima</t>
+          <t>Tudun Wada</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
@@ -3323,7 +3342,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Anka; Bakura; Bungudu; Talata Mafara</t>
+          <t>Bungudu</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -3332,13 +3351,13 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I53" t="n">
         <v>5</v>
       </c>
       <c r="J53" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
@@ -3384,10 +3403,10 @@
         <v>2</v>
       </c>
       <c r="I54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J54" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
@@ -3410,7 +3429,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Tudun Wada</t>
+          <t>Galadima</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
@@ -3421,7 +3440,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Bungudu</t>
+          <t>Anka; Bakura; Bungudu; Talata Mafara</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -3433,7 +3452,7 @@
         <v>5</v>
       </c>
       <c r="I55" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J55" t="n">
         <v>7</v>
@@ -3459,7 +3478,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Madawaki</t>
+          <t>Sabon Gari</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
@@ -3471,13 +3490,13 @@
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J56" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
@@ -3500,33 +3519,25 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Furfuri Kwaikwai</t>
+          <t>Madawaki</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>Bungudu</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr"/>
       <c r="H57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I57" t="n">
         <v>0</v>
       </c>
       <c r="J57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
@@ -3549,7 +3560,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Bela Rawaiya</t>
+          <t>Furfuri Kwaikwai</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
@@ -3560,7 +3571,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Bungudu; Kaura Namoda</t>
+          <t>Bungudu</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -3575,7 +3586,7 @@
         <v>0</v>
       </c>
       <c r="J58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
@@ -3598,7 +3609,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Bingi North</t>
+          <t>Bela Rawaiya</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
@@ -3609,7 +3620,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Bungudu; Maru</t>
+          <t>Bungudu; Kaura Namoda</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -3618,7 +3629,7 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I59" t="n">
         <v>0</v>
@@ -3647,7 +3658,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Bingi South</t>
+          <t>Bingi North</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
@@ -3696,17 +3707,25 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Dandire A</t>
+          <t>Bingi South</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr"/>
-      <c r="G61" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Bungudu; Maru</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H61" t="n">
         <v>0</v>
       </c>
@@ -3737,25 +3756,17 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Dandire B</t>
+          <t>Dandire A</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>Birnin Magaji</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr"/>
       <c r="H62" t="n">
         <v>0</v>
       </c>
@@ -3786,7 +3797,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Danjibga</t>
+          <t>Dandire B</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
@@ -3797,7 +3808,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tsafe</t>
+          <t>Birnin Magaji</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -3835,7 +3846,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Dansadau</t>
+          <t>Danjibga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
@@ -3846,7 +3857,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Maru; Tsafe</t>
+          <t>Tsafe</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -3884,17 +3895,25 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Dugu Muazu</t>
+          <t>Dansadau</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr"/>
-      <c r="G65" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Maru; Tsafe</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H65" t="n">
         <v>0</v>
       </c>
@@ -3925,25 +3944,17 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Gusami Hayi</t>
+          <t>Dugu Muazu</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>Birnin Magaji; Kaura Namoda</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr"/>
       <c r="H66" t="n">
         <v>0</v>
       </c>
@@ -3974,7 +3985,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Keta</t>
+          <t>Gusami Hayi</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
@@ -3985,7 +3996,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tsafe</t>
+          <t>Birnin Magaji; Kaura Namoda</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -4023,7 +4034,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Kotorkoshi</t>
+          <t>Keta</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
@@ -4034,7 +4045,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Bungudu; Tsafe</t>
+          <t>Tsafe</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -4072,7 +4083,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Kuyello</t>
+          <t>Kotorkoshi</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
@@ -4083,7 +4094,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Maru</t>
+          <t>Bungudu; Tsafe</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -4121,7 +4132,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Kwaren Ganuwa</t>
+          <t>Kuyello</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
@@ -4132,7 +4143,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tsafe</t>
+          <t>Maru</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -4170,7 +4181,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Mada</t>
+          <t>Kwaren Ganuwa</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
@@ -4219,7 +4230,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Magami</t>
+          <t>Mada</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
@@ -4230,7 +4241,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Bungudu; Maru; Tsafe</t>
+          <t>Tsafe</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -4268,17 +4279,25 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Maidabino B</t>
+          <t>Magami</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr"/>
-      <c r="G73" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Bungudu; Maru; Tsafe</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H73" t="n">
         <v>0</v>
       </c>
@@ -4309,25 +4328,17 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Rijiya</t>
+          <t>Maidabino B</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>Bungudu; Tsafe</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr"/>
       <c r="H74" t="n">
         <v>0</v>
       </c>
@@ -4358,17 +4369,25 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Ruwan Bore</t>
+          <t>Rijiya</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr"/>
-      <c r="G75" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Bungudu; Tsafe</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H75" t="n">
         <v>0</v>
       </c>
@@ -4399,7 +4418,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Sabon Gari</t>
+          <t>Ruwan Bore</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
@@ -4411,7 +4430,7 @@
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr"/>
       <c r="H76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I76" t="n">
         <v>0</v>
@@ -6372,7 +6391,7 @@
     </dataValidation>
     <dataValidation sqref="O2:O117" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid date" error="Enter an actual date between 01 Jul 2026 and today - click the cell and use the date picker, or type e.g. 27-Aug-2026. Free text and out-of-range dates (including future dates) are rejected here so they don't need to be caught and excluded later." type="date" operator="between">
       <formula1>2026-07-01</formula1>
-      <formula2>2026-09-20</formula2>
+      <formula2>2026-09-21</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6388,7 +6407,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O77"/>
+  <dimension ref="A1:P90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6396,16 +6415,17 @@
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="24" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="19" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="30" customWidth="1" min="12" max="12"/>
-    <col width="17" customWidth="1" min="13" max="13"/>
-    <col width="30" customWidth="1" min="14" max="14"/>
-    <col width="18" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="19" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="30" customWidth="1" min="13" max="13"/>
+    <col width="17" customWidth="1" min="14" max="14"/>
+    <col width="30" customWidth="1" min="15" max="15"/>
+    <col width="18" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6436,50 +6456,55 @@
       </c>
       <c r="F1" s="9" t="inlineStr">
         <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="G1" s="9" t="inlineStr">
+        <is>
           <t>IDP Category</t>
         </is>
       </c>
-      <c r="G1" s="9" t="inlineStr">
+      <c r="H1" s="9" t="inlineStr">
         <is>
           <t>Target HHs (primary)</t>
         </is>
       </c>
-      <c r="H1" s="9" t="inlineStr">
+      <c r="I1" s="9" t="inlineStr">
         <is>
           <t>Reserve HHs</t>
         </is>
       </c>
-      <c r="I1" s="7" t="inlineStr">
+      <c r="J1" s="7" t="inlineStr">
         <is>
           <t>Accessible (Y/N)</t>
         </is>
       </c>
-      <c r="J1" s="7" t="inlineStr">
+      <c r="K1" s="7" t="inlineStr">
         <is>
           <t>Reason category</t>
         </is>
       </c>
-      <c r="K1" s="7" t="inlineStr">
+      <c r="L1" s="7" t="inlineStr">
         <is>
           <t>Reason notes</t>
         </is>
       </c>
-      <c r="L1" s="7" t="inlineStr">
+      <c r="M1" s="7" t="inlineStr">
         <is>
           <t>% of target achieved so far</t>
         </is>
       </c>
-      <c r="M1" s="7" t="inlineStr">
+      <c r="N1" s="7" t="inlineStr">
         <is>
           <t>Date reported</t>
         </is>
       </c>
-      <c r="N1" s="7" t="inlineStr">
+      <c r="O1" s="7" t="inlineStr">
         <is>
           <t>Reported by (Partner / IMPACT-default)</t>
         </is>
       </c>
-      <c r="O1" s="7" t="inlineStr">
+      <c r="P1" s="7" t="inlineStr">
         <is>
           <t>Source channel</t>
         </is>
@@ -6513,26 +6538,31 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
           <t>In-host</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>42</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>42</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" s="10" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" s="10" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -6562,26 +6592,31 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
           <t>In-host</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="H3" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" s="10" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" s="10" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -6611,26 +6646,31 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
           <t>In-host</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" s="10" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" s="10" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -6660,26 +6700,31 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
           <t>In-host</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="H5" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" s="10" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" s="10" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -6709,26 +6754,31 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
           <t>In-host</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="H6" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" s="10" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" s="10" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -6758,26 +6808,31 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
           <t>In-host</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="H7" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" s="10" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" s="10" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -6807,26 +6862,31 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
           <t>In-camp</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="H8" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" s="10" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" s="10" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -6856,26 +6916,31 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
           <t>In-camp</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="H9" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" s="10" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" s="10" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -6903,24 +6968,29 @@
           <t>non_idp_NG008020_10</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" s="10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" s="10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -6948,24 +7018,29 @@
           <t>non_idp_NG008020_7</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" s="10" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" s="10" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -6993,24 +7068,29 @@
           <t>non_idp_NG008020_9</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" s="10" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" s="10" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -7038,24 +7118,29 @@
           <t>non_idp_NG008020_supp1</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" s="10" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" s="10" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -7083,24 +7168,29 @@
           <t>non_idp_NG008020_supp10</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" s="10" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" s="10" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -7128,24 +7218,29 @@
           <t>non_idp_NG008020_supp12</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" s="10" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" s="10" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -7173,24 +7268,29 @@
           <t>non_idp_NG008020_supp13</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" s="10" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" s="10" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -7218,24 +7318,29 @@
           <t>non_idp_NG008020_supp14</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" s="10" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" s="10" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -7263,24 +7368,29 @@
           <t>non_idp_NG008020_supp17</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" s="10" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" s="10" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -7308,24 +7418,29 @@
           <t>non_idp_NG008020_supp18</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" s="10" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" s="10" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -7353,24 +7468,29 @@
           <t>non_idp_NG008020_supp3</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" s="10" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" s="10" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -7398,24 +7518,29 @@
           <t>non_idp_NG008020_supp4</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" s="10" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" s="10" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -7443,24 +7568,29 @@
           <t>non_idp_NG008020_supp5</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" s="10" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" s="10" t="inlineStr"/>
       <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -7488,24 +7618,29 @@
           <t>non_idp_NG008020_supp6</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" s="10" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" s="10" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -7533,24 +7668,29 @@
           <t>non_idp_NG008020_supp7</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" s="10" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" s="10" t="inlineStr"/>
       <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -7580,26 +7720,31 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
           <t>In-host</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" s="10" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" s="10" t="inlineStr"/>
       <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -7629,26 +7774,31 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
           <t>In-host</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" s="10" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" s="10" t="inlineStr"/>
       <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -7678,26 +7828,31 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
           <t>In-host</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" s="10" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" s="10" t="inlineStr"/>
       <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -7727,26 +7882,31 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
           <t>In-host</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" s="10" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" s="10" t="inlineStr"/>
       <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -7776,26 +7936,31 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
           <t>In-host</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" s="10" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" s="10" t="inlineStr"/>
       <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -7825,26 +7990,31 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
           <t>In-host</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" s="10" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" s="10" t="inlineStr"/>
       <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -7874,26 +8044,31 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
           <t>In-host</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="H31" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" s="10" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" s="10" t="inlineStr"/>
       <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -7913,18 +8088,22 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>non_idp_NG008021_1</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr"/>
+          <t>idp_NG008021_supp1</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>In-host</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -7932,13 +8111,18 @@
           <t>6</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
-      <c r="M32" s="10" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" s="10" t="inlineStr"/>
       <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -7953,23 +8137,27 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Gwange 3</t>
+          <t>Mafoni</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>non_idp_NG008021_12</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr"/>
+          <t>idp_NG008021_supp2</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>In-host</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -7977,13 +8165,18 @@
           <t>6</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
-      <c r="M33" s="10" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" s="10" t="inlineStr"/>
       <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -7998,23 +8191,27 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Yajiwa</t>
+          <t>Bolori 2</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>non_idp_NG008021_13</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr"/>
+          <t>idp_NG008021_supp3</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>In-host</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -8022,13 +8219,18 @@
           <t>6</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
-      <c r="M34" s="10" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" s="10" t="inlineStr"/>
       <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -8043,37 +8245,46 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Maisandari</t>
+          <t>Bolori 2</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>non_idp_NG008021_14</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr"/>
+          <t>idp_NG008021_supp4</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>In-host</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
-      <c r="M35" s="10" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" s="10" t="inlineStr"/>
       <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -8088,37 +8299,46 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Bolori 1</t>
+          <t>Bolori 2</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>non_idp_NG008021_16</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr"/>
+          <t>idp_NG008021_supp5</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>In-host</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
-      <c r="M36" s="10" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" s="10" t="inlineStr"/>
       <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -8133,7 +8353,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Mafoni</t>
+          <t>Maisandari</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -8143,27 +8363,32 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>non_idp_NG008021_2</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+          <t>non_idp_NG008021_1</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr">
         <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
-      <c r="M37" s="10" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" s="10" t="inlineStr"/>
       <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -8178,7 +8403,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Maisandari</t>
+          <t>Gwange 3</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -8188,27 +8413,32 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>non_idp_NG008021_5</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+          <t>non_idp_NG008021_12</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr">
         <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
-      <c r="M38" s="10" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" s="10" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -8223,7 +8453,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Bolori 2</t>
+          <t>Yajiwa</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8233,27 +8463,32 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>non_idp_NG008021_8</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG008021_13</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
-      <c r="M39" s="10" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" s="10" t="inlineStr"/>
       <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -8278,419 +8513,432 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>non_idp_NG008021_9</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+          <t>non_idp_NG008021_14</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr">
         <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
-      <c r="M40" s="10" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" s="10" t="inlineStr"/>
       <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Zamfara</t>
+          <t>Borno</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Gusau</t>
+          <t>Maiduguri</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Tudun Wada</t>
+          <t>Bolori 1</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>IDP</t>
+          <t>Non-IDP</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>idp_NG037007_1</t>
+          <t>non_idp_NG008021_16</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>In-host</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
-      <c r="M41" s="10" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" s="10" t="inlineStr"/>
       <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Zamfara</t>
+          <t>Borno</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Gusau</t>
+          <t>Maiduguri</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Galadima</t>
+          <t>Mafoni</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>IDP</t>
+          <t>Non-IDP</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>idp_NG037007_11</t>
+          <t>non_idp_NG008021_2</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>In-host</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
-      <c r="M42" s="10" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" s="10" t="inlineStr"/>
       <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Zamfara</t>
+          <t>Borno</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Gusau</t>
+          <t>Maiduguri</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Tudun Wada</t>
+          <t>Maisandari</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>IDP</t>
+          <t>Non-IDP</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>idp_NG037007_13</t>
+          <t>non_idp_NG008021_5</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>In-host</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
-      <c r="M43" s="10" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" s="10" t="inlineStr"/>
       <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Zamfara</t>
+          <t>Borno</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Gusau</t>
+          <t>Maiduguri</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Galadima</t>
+          <t>Bolori 2</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>IDP</t>
+          <t>Non-IDP</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>idp_NG037007_14</t>
+          <t>non_idp_NG008021_8</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>In-host</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr">
         <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
-      <c r="M44" s="10" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" s="10" t="inlineStr"/>
       <c r="O44" t="inlineStr"/>
+      <c r="P44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Zamfara</t>
+          <t>Borno</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Gusau</t>
+          <t>Maiduguri</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Tudun Wada</t>
+          <t>Maisandari</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>IDP</t>
+          <t>Non-IDP</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>idp_NG037007_17</t>
+          <t>non_idp_NG008021_9</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>In-host</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
-      <c r="M45" s="10" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" s="10" t="inlineStr"/>
       <c r="O45" t="inlineStr"/>
+      <c r="P45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Zamfara</t>
+          <t>Borno</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Gusau</t>
+          <t>Maiduguri</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Galadima</t>
+          <t>Bolori 1</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>IDP</t>
+          <t>Non-IDP</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>idp_NG037007_8</t>
+          <t>non_idp_NG008021_supp1</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>In-host</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr">
         <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
-      <c r="M46" s="10" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" s="10" t="inlineStr"/>
       <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Zamfara</t>
+          <t>Borno</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Gusau</t>
+          <t>Maiduguri</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Galadima</t>
+          <t>Bolori 1</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>IDP</t>
+          <t>Non-IDP</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>idp_NG037007_supp1</t>
+          <t>non_idp_NG008021_supp2</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>In-host</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr"/>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
-      <c r="M47" s="10" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" s="10" t="inlineStr"/>
       <c r="O47" t="inlineStr"/>
+      <c r="P47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Zamfara</t>
+          <t>Borno</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Gusau</t>
+          <t>Maiduguri</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Mayana</t>
+          <t>Bolori 2</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>IDP</t>
+          <t>Non-IDP</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>idp_NG037007_supp2</t>
+          <t>non_idp_NG008021_supp3</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>In-host</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr"/>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
-      <c r="M48" s="10" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" s="10" t="inlineStr"/>
       <c r="O48" t="inlineStr"/>
+      <c r="P48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -8705,7 +8953,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Galadima</t>
+          <t>Tudun Wada</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8715,31 +8963,36 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>idp_NG037007_supp4</t>
+          <t>idp_NG037007_1</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
           <t>In-host</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="H49" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
-      <c r="M49" s="10" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" s="10" t="inlineStr"/>
       <c r="O49" t="inlineStr"/>
+      <c r="P49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -8754,37 +9007,46 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Tudun Wada</t>
+          <t>Galadima</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>non_idp_NG037007_1</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr"/>
+          <t>idp_NG037007_11</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>In-host</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
-      <c r="M50" s="10" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" s="10" t="inlineStr"/>
       <c r="O50" t="inlineStr"/>
+      <c r="P50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -8799,23 +9061,27 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Galadima</t>
+          <t>Tudun Wada</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>non_idp_NG037007_14</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr"/>
+          <t>idp_NG037007_13</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>In-host</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -8823,13 +9089,18 @@
           <t>6</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
-      <c r="M51" s="10" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" s="10" t="inlineStr"/>
       <c r="O51" t="inlineStr"/>
+      <c r="P51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -8844,37 +9115,46 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Tudun Wada</t>
+          <t>Galadima</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>non_idp_NG037007_15</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr"/>
+          <t>idp_NG037007_14</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>In-host</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
-      <c r="M52" s="10" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" s="10" t="inlineStr"/>
       <c r="O52" t="inlineStr"/>
+      <c r="P52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -8889,23 +9169,27 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Furfuri Kwaikwai</t>
+          <t>Tudun Wada</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>non_idp_NG037007_4</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr"/>
+          <t>idp_NG037007_17</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>In-host</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -8913,13 +9197,18 @@
           <t>6</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
-      <c r="M53" s="10" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" s="10" t="inlineStr"/>
       <c r="O53" t="inlineStr"/>
+      <c r="P53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -8934,37 +9223,46 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Madawaki</t>
+          <t>Galadima</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>non_idp_NG037007_6</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr"/>
+          <t>idp_NG037007_8</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>In-host</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
-      <c r="M54" s="10" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" s="10" t="inlineStr"/>
       <c r="O54" t="inlineStr"/>
+      <c r="P54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -8979,37 +9277,46 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Mayana</t>
+          <t>Galadima</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>non_idp_NG037007_9</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr"/>
+          <t>idp_NG037007_supp1</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>In-host</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
-      <c r="M55" s="10" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" s="10" t="inlineStr"/>
       <c r="O55" t="inlineStr"/>
+      <c r="P55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -9024,23 +9331,27 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Tudun Wada</t>
+          <t>Mayana</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>non_idp_NG037007_supp3</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr"/>
+          <t>idp_NG037007_supp2</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>In-host</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -9048,13 +9359,18 @@
           <t>6</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr"/>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
-      <c r="M56" s="10" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" s="10" t="inlineStr"/>
       <c r="O56" t="inlineStr"/>
+      <c r="P56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -9069,23 +9385,27 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Madawaki</t>
+          <t>Galadima</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>non_idp_NG037007_supp4</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr"/>
+          <t>idp_NG037007_supp4</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>In-host</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -9093,13 +9413,18 @@
           <t>6</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr"/>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
-      <c r="M57" s="10" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" s="10" t="inlineStr"/>
       <c r="O57" t="inlineStr"/>
+      <c r="P57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -9114,23 +9439,27 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Tudun Wada</t>
+          <t>Mayana</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>non_idp_NG037007_supp5</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr"/>
+          <t>idp_NG037007_supp5</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>In-host</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -9138,13 +9467,18 @@
           <t>6</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr"/>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
-      <c r="M58" s="10" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" s="10" t="inlineStr"/>
       <c r="O58" t="inlineStr"/>
+      <c r="P58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -9159,23 +9493,27 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Mayana</t>
+          <t>Sabon Gari</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>non_idp_NG037007_supp6</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr"/>
+          <t>idp_NG037007_supp6</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>In-host</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -9183,13 +9521,18 @@
           <t>6</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr"/>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
-      <c r="M59" s="10" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" s="10" t="inlineStr"/>
       <c r="O59" t="inlineStr"/>
+      <c r="P59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -9199,12 +9542,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Maru</t>
+          <t>Gusau</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Mayanchi</t>
+          <t>Tudun Wada</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -9214,31 +9557,36 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>idp_NG037010_1</t>
+          <t>idp_NG037007_supp7</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
           <t>In-host</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
-      <c r="M60" s="10" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" s="10" t="inlineStr"/>
       <c r="O60" t="inlineStr"/>
+      <c r="P60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -9248,12 +9596,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Maru</t>
+          <t>Gusau</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Maru</t>
+          <t>Tudun Wada</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -9263,31 +9611,36 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>idp_NG037010_11</t>
+          <t>idp_NG037007_supp8</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
           <t>In-host</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
-      <c r="M61" s="10" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" s="10" t="inlineStr"/>
       <c r="O61" t="inlineStr"/>
+      <c r="P61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -9297,46 +9650,47 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Maru</t>
+          <t>Gusau</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Ruwan Doruma</t>
+          <t>Tudun Wada</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>IDP</t>
+          <t>Non-IDP</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>idp_NG037010_14</t>
+          <t>non_idp_NG037007_1</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>In-host</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
-      <c r="M62" s="10" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" s="10" t="inlineStr"/>
       <c r="O62" t="inlineStr"/>
+      <c r="P62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -9346,12 +9700,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Maru</t>
+          <t>Gusau</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Ruwan Doruma</t>
+          <t>Galadima</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -9361,27 +9715,32 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>non_idp_NG037010_17</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr"/>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG037007_14</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr"/>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr"/>
-      <c r="M63" s="10" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" s="10" t="inlineStr"/>
       <c r="O63" t="inlineStr"/>
+      <c r="P63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -9391,12 +9750,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Maru</t>
+          <t>Gusau</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Maru</t>
+          <t>Tudun Wada</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -9406,27 +9765,32 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>non_idp_NG037010_supp11</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr"/>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG037007_15</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr"/>
-      <c r="M64" s="10" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" s="10" t="inlineStr"/>
       <c r="O64" t="inlineStr"/>
+      <c r="P64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -9436,12 +9800,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Maru</t>
+          <t>Gusau</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Maru</t>
+          <t>Furfuri Kwaikwai</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -9451,27 +9815,32 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>non_idp_NG037010_supp12</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr"/>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG037007_4</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr"/>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
-      <c r="M65" s="10" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" s="10" t="inlineStr"/>
       <c r="O65" t="inlineStr"/>
+      <c r="P65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -9481,12 +9850,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Maru</t>
+          <t>Gusau</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Mayanchi</t>
+          <t>Madawaki</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -9496,27 +9865,32 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>non_idp_NG037010_supp15</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr"/>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG037007_6</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
-      <c r="M66" s="10" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" s="10" t="inlineStr"/>
       <c r="O66" t="inlineStr"/>
+      <c r="P66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -9526,12 +9900,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Maru</t>
+          <t>Gusau</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Mayanchi</t>
+          <t>Mayana</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9541,27 +9915,32 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>non_idp_NG037010_supp18</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr"/>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG037007_9</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
       <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr"/>
-      <c r="M67" s="10" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" s="10" t="inlineStr"/>
       <c r="O67" t="inlineStr"/>
+      <c r="P67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -9571,12 +9950,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Maru</t>
+          <t>Gusau</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Maru</t>
+          <t>Tudun Wada</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9586,27 +9965,32 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>non_idp_NG037010_supp19</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr"/>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG037007_supp3</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr"/>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr"/>
-      <c r="M68" s="10" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" s="10" t="inlineStr"/>
       <c r="O68" t="inlineStr"/>
+      <c r="P68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -9616,12 +10000,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Maru</t>
+          <t>Gusau</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Maru</t>
+          <t>Madawaki</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9631,27 +10015,32 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>non_idp_NG037010_supp2</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr"/>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG037007_supp4</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr"/>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr"/>
-      <c r="M69" s="10" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" s="10" t="inlineStr"/>
       <c r="O69" t="inlineStr"/>
+      <c r="P69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -9661,12 +10050,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Maru</t>
+          <t>Gusau</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Maru</t>
+          <t>Tudun Wada</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9676,27 +10065,32 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>non_idp_NG037010_supp21</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr"/>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG037007_supp5</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr"/>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr"/>
-      <c r="M70" s="10" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" s="10" t="inlineStr"/>
       <c r="O70" t="inlineStr"/>
+      <c r="P70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -9706,12 +10100,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Maru</t>
+          <t>Gusau</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Ruwan Doruma</t>
+          <t>Mayana</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9721,27 +10115,32 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>non_idp_NG037010_supp25</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr"/>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG037007_supp6</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr"/>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr"/>
-      <c r="M71" s="10" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" s="10" t="inlineStr"/>
       <c r="O71" t="inlineStr"/>
+      <c r="P71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -9751,12 +10150,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Maru</t>
+          <t>Gusau</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Ruwan Doruma</t>
+          <t>Tudun Wada</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9766,27 +10165,32 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>non_idp_NG037010_supp26</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr"/>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG037007_supp8</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr"/>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr"/>
-      <c r="M72" s="10" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" s="10" t="inlineStr"/>
       <c r="O72" t="inlineStr"/>
+      <c r="P72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -9801,37 +10205,46 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Bena</t>
+          <t>Mayanchi</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>non_idp_NG037010_supp27</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr"/>
+          <t>idp_NG037010_1</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>In-host</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr"/>
-      <c r="M73" s="10" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" s="10" t="inlineStr"/>
       <c r="O73" t="inlineStr"/>
+      <c r="P73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -9846,37 +10259,46 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Mayanchi</t>
+          <t>Maru</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>non_idp_NG037010_supp28</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr"/>
+          <t>idp_NG037010_11</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>In-host</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr"/>
-      <c r="M74" s="10" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" s="10" t="inlineStr"/>
       <c r="O74" t="inlineStr"/>
+      <c r="P74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -9891,37 +10313,46 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Maru</t>
+          <t>Ruwan Doruma</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>non_idp_NG037010_supp3</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr"/>
+          <t>idp_NG037010_14</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>In-host</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr"/>
-      <c r="M75" s="10" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" s="10" t="inlineStr"/>
       <c r="O75" t="inlineStr"/>
+      <c r="P75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -9946,27 +10377,32 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>non_idp_NG037010_supp4</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr"/>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG037010_17</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr"/>
       <c r="H76" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr"/>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr"/>
-      <c r="M76" s="10" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" s="10" t="inlineStr"/>
       <c r="O76" t="inlineStr"/>
+      <c r="P76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -9991,45 +10427,700 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>non_idp_NG037010_supp6</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr"/>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG037010_supp11</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr"/>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr"/>
-      <c r="M77" s="10" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
+      <c r="M77" t="inlineStr"/>
+      <c r="N77" s="10" t="inlineStr"/>
       <c r="O77" t="inlineStr"/>
+      <c r="P77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Maru</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Maru</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>non_idp_NG037010_supp12</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr"/>
+      <c r="N78" s="10" t="inlineStr"/>
+      <c r="O78" t="inlineStr"/>
+      <c r="P78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Maru</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Mayanchi</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>non_idp_NG037010_supp15</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr"/>
+      <c r="N79" s="10" t="inlineStr"/>
+      <c r="O79" t="inlineStr"/>
+      <c r="P79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Maru</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Mayanchi</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>non_idp_NG037010_supp18</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr"/>
+      <c r="N80" s="10" t="inlineStr"/>
+      <c r="O80" t="inlineStr"/>
+      <c r="P80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Maru</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Maru</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>non_idp_NG037010_supp19</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr"/>
+      <c r="N81" s="10" t="inlineStr"/>
+      <c r="O81" t="inlineStr"/>
+      <c r="P81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Maru</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Maru</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>non_idp_NG037010_supp2</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr"/>
+      <c r="N82" s="10" t="inlineStr"/>
+      <c r="O82" t="inlineStr"/>
+      <c r="P82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Maru</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Maru</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>non_idp_NG037010_supp21</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr"/>
+      <c r="N83" s="10" t="inlineStr"/>
+      <c r="O83" t="inlineStr"/>
+      <c r="P83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Maru</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Ruwan Doruma</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>non_idp_NG037010_supp25</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr"/>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr"/>
+      <c r="N84" s="10" t="inlineStr"/>
+      <c r="O84" t="inlineStr"/>
+      <c r="P84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Maru</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Ruwan Doruma</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>non_idp_NG037010_supp26</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr"/>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr"/>
+      <c r="N85" s="10" t="inlineStr"/>
+      <c r="O85" t="inlineStr"/>
+      <c r="P85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Maru</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Bena</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>non_idp_NG037010_supp27</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr"/>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr"/>
+      <c r="N86" s="10" t="inlineStr"/>
+      <c r="O86" t="inlineStr"/>
+      <c r="P86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Maru</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Mayanchi</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>non_idp_NG037010_supp28</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr"/>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr"/>
+      <c r="N87" s="10" t="inlineStr"/>
+      <c r="O87" t="inlineStr"/>
+      <c r="P87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Maru</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Maru</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>non_idp_NG037010_supp3</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr"/>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr"/>
+      <c r="N88" s="10" t="inlineStr"/>
+      <c r="O88" t="inlineStr"/>
+      <c r="P88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Maru</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Ruwan Doruma</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>non_idp_NG037010_supp4</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr"/>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr"/>
+      <c r="N89" s="10" t="inlineStr"/>
+      <c r="O89" t="inlineStr"/>
+      <c r="P89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Maru</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Maru</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>non_idp_NG037010_supp6</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr"/>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr"/>
+      <c r="N90" s="10" t="inlineStr"/>
+      <c r="O90" t="inlineStr"/>
+      <c r="P90" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="5">
-    <dataValidation sqref="I2:I77" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J2:J90" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation sqref="J2:J77" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="K2:K90" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"N/A - fully accessible,Insecurity / conflict,Physical access (terrain, flooding, roads),Population absent / relocated,Building-footprint issue (no eligible structures),Access denied by authorities / community,Other"</formula1>
     </dataValidation>
-    <dataValidation sqref="N2:N77" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="O2:O90" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Partner,IMPACT (default - accessible until reported otherwise)"</formula1>
     </dataValidation>
-    <dataValidation sqref="O2:O77" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="P2:P90" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Partner's own template,Email,WhatsApp/verbal (coordinator-transcribed),Point-level file annotation,N/A"</formula1>
     </dataValidation>
-    <dataValidation sqref="M2:M77" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid date" error="Enter an actual date between 01 Jul 2026 and today - click the cell and use the date picker, or type e.g. 27-Aug-2026. Free text and out-of-range dates (including future dates) are rejected here so they don't need to be caught and excluded later." type="date" operator="between">
+    <dataValidation sqref="N2:N90" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid date" error="Enter an actual date between 01 Jul 2026 and today - click the cell and use the date picker, or type e.g. 27-Aug-2026. Free text and out-of-range dates (including future dates) are rejected here so they don't need to be caught and excluded later." type="date" operator="between">
       <formula1>2026-07-01</formula1>
-      <formula2>2026-09-20</formula2>
+      <formula2>2026-09-21</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10295,13 +11386,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CFE27A73-B6E5-4420-A570-7D68432808DC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9249BB27-EA97-4B2A-83A1-9770FF83E190}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D56A8D02-B362-4C12-A0AB-7D97BFDF7F56}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{95C89A45-DBB2-4D57-BF95-5CE3C9F9F624}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2221AB51-CA71-4DA6-A300-54039FF6D688}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BB7A2392-8645-48FC-BAE2-99B7861E2499}"/>
 </file>